--- a/data/city_crosswalk.xlsx
+++ b/data/city_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\OneDrive\Desktop\Bobby\GitHub\Skyscrapers\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECB1E94-1689-41B3-B5C7-BCF6B56F34C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243FD9A1-E007-4BEF-A24C-78E26E4FC117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{96C4E9D1-39CB-4160-B661-174130F89492}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Crosswalk" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Crosswalk!$A$1:$C$773</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Crosswalk!$A$1:$C$782</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
     <definedName name="IQ_CY">10000</definedName>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="1648">
   <si>
     <t>name_city</t>
   </si>
@@ -7084,6 +7084,36 @@
   </si>
   <si>
     <t>Pearl River Delta</t>
+  </si>
+  <si>
+    <t>Nacka</t>
+  </si>
+  <si>
+    <t>Sigtuna</t>
+  </si>
+  <si>
+    <t>Sollentuna</t>
+  </si>
+  <si>
+    <t>Taby</t>
+  </si>
+  <si>
+    <t>Upplands Vasby</t>
+  </si>
+  <si>
+    <t>Stanford</t>
+  </si>
+  <si>
+    <t>San Francisco Bay Area</t>
+  </si>
+  <si>
+    <t>Osan</t>
+  </si>
+  <si>
+    <t>Pyeongtaek</t>
+  </si>
+  <si>
+    <t>Yeoju</t>
   </si>
 </sst>
 </file>
@@ -21381,6 +21411,99 @@
     </row>
   </sheetData>
   <mergeCells count="105">
+    <mergeCell ref="A947:D947"/>
+    <mergeCell ref="A952:D952"/>
+    <mergeCell ref="A966:D966"/>
+    <mergeCell ref="A896:D896"/>
+    <mergeCell ref="A903:D903"/>
+    <mergeCell ref="A912:D912"/>
+    <mergeCell ref="A922:D922"/>
+    <mergeCell ref="A926:D926"/>
+    <mergeCell ref="A930:D930"/>
+    <mergeCell ref="A843:D843"/>
+    <mergeCell ref="A866:D866"/>
+    <mergeCell ref="A871:D871"/>
+    <mergeCell ref="A878:D878"/>
+    <mergeCell ref="A884:D884"/>
+    <mergeCell ref="A888:D888"/>
+    <mergeCell ref="A777:D777"/>
+    <mergeCell ref="A795:D795"/>
+    <mergeCell ref="A799:D799"/>
+    <mergeCell ref="A808:D808"/>
+    <mergeCell ref="A835:D835"/>
+    <mergeCell ref="A839:D839"/>
+    <mergeCell ref="A740:D740"/>
+    <mergeCell ref="A744:D744"/>
+    <mergeCell ref="A748:D748"/>
+    <mergeCell ref="A752:D752"/>
+    <mergeCell ref="A756:D756"/>
+    <mergeCell ref="A769:D769"/>
+    <mergeCell ref="A710:D710"/>
+    <mergeCell ref="A714:D714"/>
+    <mergeCell ref="A718:D718"/>
+    <mergeCell ref="A726:D726"/>
+    <mergeCell ref="A730:D730"/>
+    <mergeCell ref="A736:D736"/>
+    <mergeCell ref="A617:D617"/>
+    <mergeCell ref="A625:D625"/>
+    <mergeCell ref="A629:D629"/>
+    <mergeCell ref="A683:D683"/>
+    <mergeCell ref="A695:D695"/>
+    <mergeCell ref="A702:D702"/>
+    <mergeCell ref="A561:D561"/>
+    <mergeCell ref="A566:D566"/>
+    <mergeCell ref="A570:D570"/>
+    <mergeCell ref="A601:D601"/>
+    <mergeCell ref="A605:D605"/>
+    <mergeCell ref="A612:D612"/>
+    <mergeCell ref="A514:D514"/>
+    <mergeCell ref="A518:D518"/>
+    <mergeCell ref="A525:D525"/>
+    <mergeCell ref="A531:D531"/>
+    <mergeCell ref="A552:D552"/>
+    <mergeCell ref="A556:D556"/>
+    <mergeCell ref="A446:D446"/>
+    <mergeCell ref="A451:D451"/>
+    <mergeCell ref="A466:D466"/>
+    <mergeCell ref="A470:D470"/>
+    <mergeCell ref="A478:D478"/>
+    <mergeCell ref="A493:D493"/>
+    <mergeCell ref="A394:D394"/>
+    <mergeCell ref="A399:D399"/>
+    <mergeCell ref="A404:D404"/>
+    <mergeCell ref="A410:D410"/>
+    <mergeCell ref="A416:D416"/>
+    <mergeCell ref="A442:D442"/>
+    <mergeCell ref="A347:D347"/>
+    <mergeCell ref="A360:D360"/>
+    <mergeCell ref="A366:D366"/>
+    <mergeCell ref="A373:D373"/>
+    <mergeCell ref="A378:D378"/>
+    <mergeCell ref="A382:D382"/>
+    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A314:D314"/>
+    <mergeCell ref="A327:D327"/>
+    <mergeCell ref="A332:D332"/>
+    <mergeCell ref="A338:D338"/>
+    <mergeCell ref="A342:D342"/>
+    <mergeCell ref="A262:D262"/>
+    <mergeCell ref="A266:D266"/>
+    <mergeCell ref="A271:D271"/>
+    <mergeCell ref="A275:D275"/>
+    <mergeCell ref="A286:D286"/>
+    <mergeCell ref="A290:D290"/>
+    <mergeCell ref="A202:D202"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="A223:D223"/>
+    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A240:D240"/>
+    <mergeCell ref="A253:D253"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A186:D186"/>
+    <mergeCell ref="A198:D198"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A68:D68"/>
@@ -21393,99 +21516,6 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A202:D202"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A223:D223"/>
-    <mergeCell ref="A236:D236"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="A253:D253"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A175:D175"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A198:D198"/>
-    <mergeCell ref="A310:D310"/>
-    <mergeCell ref="A314:D314"/>
-    <mergeCell ref="A327:D327"/>
-    <mergeCell ref="A332:D332"/>
-    <mergeCell ref="A338:D338"/>
-    <mergeCell ref="A342:D342"/>
-    <mergeCell ref="A262:D262"/>
-    <mergeCell ref="A266:D266"/>
-    <mergeCell ref="A271:D271"/>
-    <mergeCell ref="A275:D275"/>
-    <mergeCell ref="A286:D286"/>
-    <mergeCell ref="A290:D290"/>
-    <mergeCell ref="A394:D394"/>
-    <mergeCell ref="A399:D399"/>
-    <mergeCell ref="A404:D404"/>
-    <mergeCell ref="A410:D410"/>
-    <mergeCell ref="A416:D416"/>
-    <mergeCell ref="A442:D442"/>
-    <mergeCell ref="A347:D347"/>
-    <mergeCell ref="A360:D360"/>
-    <mergeCell ref="A366:D366"/>
-    <mergeCell ref="A373:D373"/>
-    <mergeCell ref="A378:D378"/>
-    <mergeCell ref="A382:D382"/>
-    <mergeCell ref="A514:D514"/>
-    <mergeCell ref="A518:D518"/>
-    <mergeCell ref="A525:D525"/>
-    <mergeCell ref="A531:D531"/>
-    <mergeCell ref="A552:D552"/>
-    <mergeCell ref="A556:D556"/>
-    <mergeCell ref="A446:D446"/>
-    <mergeCell ref="A451:D451"/>
-    <mergeCell ref="A466:D466"/>
-    <mergeCell ref="A470:D470"/>
-    <mergeCell ref="A478:D478"/>
-    <mergeCell ref="A493:D493"/>
-    <mergeCell ref="A617:D617"/>
-    <mergeCell ref="A625:D625"/>
-    <mergeCell ref="A629:D629"/>
-    <mergeCell ref="A683:D683"/>
-    <mergeCell ref="A695:D695"/>
-    <mergeCell ref="A702:D702"/>
-    <mergeCell ref="A561:D561"/>
-    <mergeCell ref="A566:D566"/>
-    <mergeCell ref="A570:D570"/>
-    <mergeCell ref="A601:D601"/>
-    <mergeCell ref="A605:D605"/>
-    <mergeCell ref="A612:D612"/>
-    <mergeCell ref="A740:D740"/>
-    <mergeCell ref="A744:D744"/>
-    <mergeCell ref="A748:D748"/>
-    <mergeCell ref="A752:D752"/>
-    <mergeCell ref="A756:D756"/>
-    <mergeCell ref="A769:D769"/>
-    <mergeCell ref="A710:D710"/>
-    <mergeCell ref="A714:D714"/>
-    <mergeCell ref="A718:D718"/>
-    <mergeCell ref="A726:D726"/>
-    <mergeCell ref="A730:D730"/>
-    <mergeCell ref="A736:D736"/>
-    <mergeCell ref="A843:D843"/>
-    <mergeCell ref="A866:D866"/>
-    <mergeCell ref="A871:D871"/>
-    <mergeCell ref="A878:D878"/>
-    <mergeCell ref="A884:D884"/>
-    <mergeCell ref="A888:D888"/>
-    <mergeCell ref="A777:D777"/>
-    <mergeCell ref="A795:D795"/>
-    <mergeCell ref="A799:D799"/>
-    <mergeCell ref="A808:D808"/>
-    <mergeCell ref="A835:D835"/>
-    <mergeCell ref="A839:D839"/>
-    <mergeCell ref="A947:D947"/>
-    <mergeCell ref="A952:D952"/>
-    <mergeCell ref="A966:D966"/>
-    <mergeCell ref="A896:D896"/>
-    <mergeCell ref="A903:D903"/>
-    <mergeCell ref="A912:D912"/>
-    <mergeCell ref="A922:D922"/>
-    <mergeCell ref="A926:D926"/>
-    <mergeCell ref="A930:D930"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://skyscraperpage.com/cities/?cityID=149" xr:uid="{DD369ABA-25BD-4D20-89A5-33EC39EDAA77}"/>
@@ -23396,7 +23426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38210FFA-F41E-4694-9E11-07D3D8230991}">
-  <dimension ref="A1:C773"/>
+  <dimension ref="A1:C782"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -29227,8 +29257,8 @@
       <c r="A530" t="s">
         <v>1603</v>
       </c>
-      <c r="B530" t="e">
-        <v>#N/A</v>
+      <c r="B530">
+        <v>3560</v>
       </c>
       <c r="C530" t="s">
         <v>1131</v>
@@ -29238,8 +29268,8 @@
       <c r="A531" t="s">
         <v>1130</v>
       </c>
-      <c r="B531" t="e">
-        <v>#N/A</v>
+      <c r="B531">
+        <v>1447</v>
       </c>
       <c r="C531" t="s">
         <v>1131</v>
@@ -29249,8 +29279,8 @@
       <c r="A532" t="s">
         <v>1131</v>
       </c>
-      <c r="B532" t="e">
-        <v>#N/A</v>
+      <c r="B532">
+        <v>326</v>
       </c>
       <c r="C532" t="s">
         <v>1131</v>
@@ -29282,8 +29312,8 @@
       <c r="A535" t="s">
         <v>1132</v>
       </c>
-      <c r="B535" t="e">
-        <v>#N/A</v>
+      <c r="B535">
+        <v>165</v>
       </c>
       <c r="C535" t="s">
         <v>1133</v>
@@ -29293,8 +29323,8 @@
       <c r="A536" t="s">
         <v>1133</v>
       </c>
-      <c r="B536" t="e">
-        <v>#N/A</v>
+      <c r="B536">
+        <v>164</v>
       </c>
       <c r="C536" t="s">
         <v>1133</v>
@@ -29304,8 +29334,8 @@
       <c r="A537" t="s">
         <v>1134</v>
       </c>
-      <c r="B537" t="e">
-        <v>#N/A</v>
+      <c r="B537">
+        <v>3157</v>
       </c>
       <c r="C537" t="s">
         <v>1133</v>
@@ -29315,8 +29345,8 @@
       <c r="A538" t="s">
         <v>1135</v>
       </c>
-      <c r="B538" t="e">
-        <v>#N/A</v>
+      <c r="B538">
+        <v>2821</v>
       </c>
       <c r="C538" t="s">
         <v>1133</v>
@@ -29326,8 +29356,8 @@
       <c r="A539" t="s">
         <v>1136</v>
       </c>
-      <c r="B539" t="e">
-        <v>#N/A</v>
+      <c r="B539">
+        <v>6133</v>
       </c>
       <c r="C539" t="s">
         <v>1137</v>
@@ -29337,8 +29367,8 @@
       <c r="A540" t="s">
         <v>1137</v>
       </c>
-      <c r="B540" t="e">
-        <v>#N/A</v>
+      <c r="B540">
+        <v>327</v>
       </c>
       <c r="C540" t="s">
         <v>1137</v>
@@ -29425,8 +29455,8 @@
       <c r="A548" t="s">
         <v>1138</v>
       </c>
-      <c r="B548" t="e">
-        <v>#N/A</v>
+      <c r="B548">
+        <v>6879</v>
       </c>
       <c r="C548" t="s">
         <v>1139</v>
@@ -29436,8 +29466,8 @@
       <c r="A549" t="s">
         <v>1139</v>
       </c>
-      <c r="B549" t="e">
-        <v>#N/A</v>
+      <c r="B549">
+        <v>1378</v>
       </c>
       <c r="C549" t="s">
         <v>1139</v>
@@ -29447,8 +29477,8 @@
       <c r="A550" t="s">
         <v>1140</v>
       </c>
-      <c r="B550" t="e">
-        <v>#N/A</v>
+      <c r="B550">
+        <v>7655</v>
       </c>
       <c r="C550" t="s">
         <v>1139</v>
@@ -29458,8 +29488,8 @@
       <c r="A551" t="s">
         <v>1607</v>
       </c>
-      <c r="B551" t="e">
-        <v>#N/A</v>
+      <c r="B551">
+        <v>4255</v>
       </c>
       <c r="C551" t="s">
         <v>1139</v>
@@ -29469,8 +29499,8 @@
       <c r="A552" t="s">
         <v>1608</v>
       </c>
-      <c r="B552" t="e">
-        <v>#N/A</v>
+      <c r="B552">
+        <v>3615</v>
       </c>
       <c r="C552" t="s">
         <v>1139</v>
@@ -29480,8 +29510,8 @@
       <c r="A553" t="s">
         <v>1141</v>
       </c>
-      <c r="B553" t="e">
-        <v>#N/A</v>
+      <c r="B553">
+        <v>3600</v>
       </c>
       <c r="C553" t="s">
         <v>1142</v>
@@ -29491,8 +29521,8 @@
       <c r="A554" t="s">
         <v>1142</v>
       </c>
-      <c r="B554" t="e">
-        <v>#N/A</v>
+      <c r="B554">
+        <v>2098</v>
       </c>
       <c r="C554" t="s">
         <v>1142</v>
@@ -29502,8 +29532,8 @@
       <c r="A555" t="s">
         <v>1143</v>
       </c>
-      <c r="B555" t="e">
-        <v>#N/A</v>
+      <c r="B555">
+        <v>7933</v>
       </c>
       <c r="C555" t="s">
         <v>1145</v>
@@ -29513,8 +29543,8 @@
       <c r="A556" t="s">
         <v>1144</v>
       </c>
-      <c r="B556" t="e">
-        <v>#N/A</v>
+      <c r="B556">
+        <v>6473</v>
       </c>
       <c r="C556" t="s">
         <v>1145</v>
@@ -29524,8 +29554,8 @@
       <c r="A557" t="s">
         <v>1145</v>
       </c>
-      <c r="B557" t="e">
-        <v>#N/A</v>
+      <c r="B557">
+        <v>65</v>
       </c>
       <c r="C557" t="s">
         <v>1145</v>
@@ -29535,8 +29565,8 @@
       <c r="A558" t="s">
         <v>1146</v>
       </c>
-      <c r="B558" t="e">
-        <v>#N/A</v>
+      <c r="B558">
+        <v>8105</v>
       </c>
       <c r="C558" t="s">
         <v>1145</v>
@@ -29546,8 +29576,8 @@
       <c r="A559" t="s">
         <v>1609</v>
       </c>
-      <c r="B559" t="e">
-        <v>#N/A</v>
+      <c r="B559">
+        <v>2454</v>
       </c>
       <c r="C559" t="s">
         <v>1147</v>
@@ -29557,8 +29587,8 @@
       <c r="A560" t="s">
         <v>1147</v>
       </c>
-      <c r="B560" t="e">
-        <v>#N/A</v>
+      <c r="B560">
+        <v>2453</v>
       </c>
       <c r="C560" t="s">
         <v>1147</v>
@@ -29568,8 +29598,8 @@
       <c r="A561" t="s">
         <v>1148</v>
       </c>
-      <c r="B561" t="e">
-        <v>#N/A</v>
+      <c r="B561">
+        <v>3362</v>
       </c>
       <c r="C561" t="s">
         <v>1148</v>
@@ -29579,8 +29609,8 @@
       <c r="A562" t="s">
         <v>1149</v>
       </c>
-      <c r="B562" t="e">
-        <v>#N/A</v>
+      <c r="B562">
+        <v>7656</v>
       </c>
       <c r="C562" t="s">
         <v>1148</v>
@@ -29590,8 +29620,8 @@
       <c r="A563" t="s">
         <v>1150</v>
       </c>
-      <c r="B563" t="e">
-        <v>#N/A</v>
+      <c r="B563">
+        <v>162</v>
       </c>
       <c r="C563" t="s">
         <v>1150</v>
@@ -29601,8 +29631,8 @@
       <c r="A564" t="s">
         <v>1151</v>
       </c>
-      <c r="B564" t="e">
-        <v>#N/A</v>
+      <c r="B564">
+        <v>4237</v>
       </c>
       <c r="C564" t="s">
         <v>1150</v>
@@ -29612,8 +29642,8 @@
       <c r="A565" t="s">
         <v>1152</v>
       </c>
-      <c r="B565" t="e">
-        <v>#N/A</v>
+      <c r="B565">
+        <v>1211</v>
       </c>
       <c r="C565" t="s">
         <v>1153</v>
@@ -29623,8 +29653,8 @@
       <c r="A566" t="s">
         <v>1153</v>
       </c>
-      <c r="B566" t="e">
-        <v>#N/A</v>
+      <c r="B566">
+        <v>893</v>
       </c>
       <c r="C566" t="s">
         <v>1153</v>
@@ -29634,8 +29664,8 @@
       <c r="A567" t="s">
         <v>1154</v>
       </c>
-      <c r="B567" t="e">
-        <v>#N/A</v>
+      <c r="B567">
+        <v>3901</v>
       </c>
       <c r="C567" t="s">
         <v>1155</v>
@@ -29645,8 +29675,8 @@
       <c r="A568" t="s">
         <v>1155</v>
       </c>
-      <c r="B568" t="e">
-        <v>#N/A</v>
+      <c r="B568">
+        <v>3390</v>
       </c>
       <c r="C568" t="s">
         <v>1155</v>
@@ -29678,8 +29708,8 @@
       <c r="A571" t="s">
         <v>1158</v>
       </c>
-      <c r="B571" t="e">
-        <v>#N/A</v>
+      <c r="B571">
+        <v>1908</v>
       </c>
       <c r="C571" t="s">
         <v>1162</v>
@@ -29689,8 +29719,8 @@
       <c r="A572" t="s">
         <v>1159</v>
       </c>
-      <c r="B572" t="e">
-        <v>#N/A</v>
+      <c r="B572">
+        <v>2609</v>
       </c>
       <c r="C572" t="s">
         <v>1162</v>
@@ -29700,8 +29730,8 @@
       <c r="A573" t="s">
         <v>1160</v>
       </c>
-      <c r="B573" t="e">
-        <v>#N/A</v>
+      <c r="B573">
+        <v>1087</v>
       </c>
       <c r="C573" t="s">
         <v>1162</v>
@@ -29711,8 +29741,8 @@
       <c r="A574" t="s">
         <v>1161</v>
       </c>
-      <c r="B574" t="e">
-        <v>#N/A</v>
+      <c r="B574">
+        <v>1691</v>
       </c>
       <c r="C574" t="s">
         <v>1162</v>
@@ -29722,8 +29752,8 @@
       <c r="A575" t="s">
         <v>1162</v>
       </c>
-      <c r="B575" t="e">
-        <v>#N/A</v>
+      <c r="B575">
+        <v>897</v>
       </c>
       <c r="C575" t="s">
         <v>1162</v>
@@ -29733,8 +29763,8 @@
       <c r="A576" t="s">
         <v>1163</v>
       </c>
-      <c r="B576" t="e">
-        <v>#N/A</v>
+      <c r="B576">
+        <v>2373</v>
       </c>
       <c r="C576" t="s">
         <v>1162</v>
@@ -29744,8 +29774,8 @@
       <c r="A577" t="s">
         <v>1164</v>
       </c>
-      <c r="B577" t="e">
-        <v>#N/A</v>
+      <c r="B577">
+        <v>1102</v>
       </c>
       <c r="C577" t="s">
         <v>1162</v>
@@ -29755,8 +29785,8 @@
       <c r="A578" t="s">
         <v>1165</v>
       </c>
-      <c r="B578" t="e">
-        <v>#N/A</v>
+      <c r="B578">
+        <v>3610</v>
       </c>
       <c r="C578" t="s">
         <v>1162</v>
@@ -29766,8 +29796,8 @@
       <c r="A579" t="s">
         <v>1610</v>
       </c>
-      <c r="B579" t="e">
-        <v>#N/A</v>
+      <c r="B579">
+        <v>3436</v>
       </c>
       <c r="C579" t="s">
         <v>1162</v>
@@ -29788,8 +29818,8 @@
       <c r="A581" t="s">
         <v>1166</v>
       </c>
-      <c r="B581" t="e">
-        <v>#N/A</v>
+      <c r="B581">
+        <v>397</v>
       </c>
       <c r="C581" t="s">
         <v>1168</v>
@@ -29799,8 +29829,8 @@
       <c r="A582" t="s">
         <v>1167</v>
       </c>
-      <c r="B582" t="e">
-        <v>#N/A</v>
+      <c r="B582">
+        <v>91</v>
       </c>
       <c r="C582" t="s">
         <v>1168</v>
@@ -29810,8 +29840,8 @@
       <c r="A583" t="s">
         <v>1168</v>
       </c>
-      <c r="B583" t="e">
-        <v>#N/A</v>
+      <c r="B583">
+        <v>90</v>
       </c>
       <c r="C583" t="s">
         <v>1168</v>
@@ -29821,8 +29851,8 @@
       <c r="A584" t="s">
         <v>1612</v>
       </c>
-      <c r="B584" t="e">
-        <v>#N/A</v>
+      <c r="B584">
+        <v>6941</v>
       </c>
       <c r="C584" t="s">
         <v>1168</v>
@@ -29832,8 +29862,8 @@
       <c r="A585" t="s">
         <v>1613</v>
       </c>
-      <c r="B585" t="e">
-        <v>#N/A</v>
+      <c r="B585">
+        <v>391</v>
       </c>
       <c r="C585" t="s">
         <v>1168</v>
@@ -29847,7 +29877,7 @@
         <v>209</v>
       </c>
       <c r="C586" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -29858,7 +29888,7 @@
         <v>5029</v>
       </c>
       <c r="C587" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -29869,169 +29899,169 @@
         <v>6055</v>
       </c>
       <c r="C588" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1172</v>
       </c>
-      <c r="B589" t="e">
-        <v>#N/A</v>
+      <c r="B589">
+        <v>5025</v>
       </c>
       <c r="C589" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>1614</v>
       </c>
-      <c r="B590" t="e">
-        <v>#N/A</v>
+      <c r="B590">
+        <v>6058</v>
       </c>
       <c r="C590" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>1173</v>
       </c>
-      <c r="B591" t="e">
-        <v>#N/A</v>
+      <c r="B591">
+        <v>5018</v>
       </c>
       <c r="C591" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>1174</v>
       </c>
-      <c r="B592" t="e">
-        <v>#N/A</v>
+      <c r="B592">
+        <v>113</v>
       </c>
       <c r="C592" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1175</v>
       </c>
-      <c r="B593" t="e">
-        <v>#N/A</v>
+      <c r="B593">
+        <v>3836</v>
       </c>
       <c r="C593" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>897</v>
       </c>
-      <c r="B594" t="e">
-        <v>#N/A</v>
+      <c r="B594">
+        <v>128</v>
       </c>
       <c r="C594" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1176</v>
       </c>
-      <c r="B595" t="e">
-        <v>#N/A</v>
+      <c r="B595">
+        <v>114</v>
       </c>
       <c r="C595" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1177</v>
       </c>
-      <c r="B596" t="e">
-        <v>#N/A</v>
+      <c r="B596">
+        <v>123</v>
       </c>
       <c r="C596" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1178</v>
       </c>
-      <c r="B597" t="e">
-        <v>#N/A</v>
+      <c r="B597">
+        <v>5017</v>
       </c>
       <c r="C597" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1179</v>
       </c>
-      <c r="B598" t="e">
-        <v>#N/A</v>
+      <c r="B598">
+        <v>3414</v>
       </c>
       <c r="C598" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1180</v>
       </c>
-      <c r="B599" t="e">
-        <v>#N/A</v>
+      <c r="B599">
+        <v>5014</v>
       </c>
       <c r="C599" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B600" t="e">
-        <v>#N/A</v>
+        <v>1643</v>
+      </c>
+      <c r="B600">
+        <v>124</v>
       </c>
       <c r="C600" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B601" t="e">
-        <v>#N/A</v>
+        <v>1181</v>
+      </c>
+      <c r="B601">
+        <v>215</v>
       </c>
       <c r="C601" t="s">
-        <v>1176</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B602">
-        <v>2224</v>
+        <v>220</v>
       </c>
       <c r="C602" t="s">
-        <v>1184</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B603" t="e">
-        <v>#N/A</v>
+        <v>1183</v>
+      </c>
+      <c r="B603">
+        <v>2224</v>
       </c>
       <c r="C603" t="s">
         <v>1184</v>
@@ -30039,21 +30069,21 @@
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B604">
-        <v>83</v>
+        <v>909</v>
       </c>
       <c r="C604" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B605" t="e">
-        <v>#N/A</v>
+        <v>1185</v>
+      </c>
+      <c r="B605">
+        <v>83</v>
       </c>
       <c r="C605" t="s">
         <v>1189</v>
@@ -30061,10 +30091,10 @@
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>1615</v>
-      </c>
-      <c r="B606" t="e">
-        <v>#N/A</v>
+        <v>1186</v>
+      </c>
+      <c r="B606">
+        <v>1331</v>
       </c>
       <c r="C606" t="s">
         <v>1189</v>
@@ -30072,10 +30102,10 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B607" t="e">
-        <v>#N/A</v>
+        <v>1615</v>
+      </c>
+      <c r="B607">
+        <v>1332</v>
       </c>
       <c r="C607" t="s">
         <v>1189</v>
@@ -30083,10 +30113,10 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B608" t="e">
-        <v>#N/A</v>
+        <v>1187</v>
+      </c>
+      <c r="B608">
+        <v>1327</v>
       </c>
       <c r="C608" t="s">
         <v>1189</v>
@@ -30094,10 +30124,10 @@
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B609" t="e">
-        <v>#N/A</v>
+        <v>1188</v>
+      </c>
+      <c r="B609">
+        <v>406</v>
       </c>
       <c r="C609" t="s">
         <v>1189</v>
@@ -30105,10 +30135,10 @@
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B610" t="e">
-        <v>#N/A</v>
+        <v>1189</v>
+      </c>
+      <c r="B610">
+        <v>27</v>
       </c>
       <c r="C610" t="s">
         <v>1189</v>
@@ -30116,21 +30146,21 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B611">
-        <v>7503</v>
+        <v>79</v>
       </c>
       <c r="C611" t="s">
-        <v>1209</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B612">
-        <v>8737</v>
+        <v>7503</v>
       </c>
       <c r="C612" t="s">
         <v>1209</v>
@@ -30138,10 +30168,10 @@
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B613">
-        <v>2833</v>
+        <v>8737</v>
       </c>
       <c r="C613" t="s">
         <v>1209</v>
@@ -30149,10 +30179,10 @@
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B614">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="C614" t="s">
         <v>1209</v>
@@ -30160,10 +30190,10 @@
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B615">
-        <v>1749</v>
+        <v>2836</v>
       </c>
       <c r="C615" t="s">
         <v>1209</v>
@@ -30171,10 +30201,10 @@
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B616" t="e">
-        <v>#N/A</v>
+        <v>1195</v>
+      </c>
+      <c r="B616">
+        <v>1749</v>
       </c>
       <c r="C616" t="s">
         <v>1209</v>
@@ -30182,10 +30212,10 @@
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B617" t="e">
-        <v>#N/A</v>
+        <v>1196</v>
+      </c>
+      <c r="B617">
+        <v>7505</v>
       </c>
       <c r="C617" t="s">
         <v>1209</v>
@@ -30193,10 +30223,10 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B618" t="e">
-        <v>#N/A</v>
+        <v>1197</v>
+      </c>
+      <c r="B618">
+        <v>1759</v>
       </c>
       <c r="C618" t="s">
         <v>1209</v>
@@ -30204,10 +30234,10 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B619" t="e">
-        <v>#N/A</v>
+        <v>1198</v>
+      </c>
+      <c r="B619">
+        <v>2834</v>
       </c>
       <c r="C619" t="s">
         <v>1209</v>
@@ -30215,10 +30245,10 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B620" t="e">
-        <v>#N/A</v>
+        <v>1199</v>
+      </c>
+      <c r="B620">
+        <v>7476</v>
       </c>
       <c r="C620" t="s">
         <v>1209</v>
@@ -30226,10 +30256,10 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B621" t="e">
-        <v>#N/A</v>
+        <v>1200</v>
+      </c>
+      <c r="B621">
+        <v>1765</v>
       </c>
       <c r="C621" t="s">
         <v>1209</v>
@@ -30237,10 +30267,10 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B622" t="e">
-        <v>#N/A</v>
+        <v>1201</v>
+      </c>
+      <c r="B622">
+        <v>7480</v>
       </c>
       <c r="C622" t="s">
         <v>1209</v>
@@ -30248,10 +30278,10 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B623" t="e">
-        <v>#N/A</v>
+        <v>1202</v>
+      </c>
+      <c r="B623">
+        <v>7481</v>
       </c>
       <c r="C623" t="s">
         <v>1209</v>
@@ -30259,10 +30289,10 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B624" t="e">
-        <v>#N/A</v>
+        <v>1203</v>
+      </c>
+      <c r="B624">
+        <v>5488</v>
       </c>
       <c r="C624" t="s">
         <v>1209</v>
@@ -30270,10 +30300,10 @@
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B625" t="e">
-        <v>#N/A</v>
+        <v>1204</v>
+      </c>
+      <c r="B625">
+        <v>6646</v>
       </c>
       <c r="C625" t="s">
         <v>1209</v>
@@ -30281,10 +30311,10 @@
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B626" t="e">
-        <v>#N/A</v>
+        <v>1205</v>
+      </c>
+      <c r="B626">
+        <v>1756</v>
       </c>
       <c r="C626" t="s">
         <v>1209</v>
@@ -30292,10 +30322,10 @@
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B627" t="e">
-        <v>#N/A</v>
+        <v>1206</v>
+      </c>
+      <c r="B627">
+        <v>5511</v>
       </c>
       <c r="C627" t="s">
         <v>1209</v>
@@ -30303,10 +30333,10 @@
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B628" t="e">
-        <v>#N/A</v>
+        <v>1645</v>
+      </c>
+      <c r="B628">
+        <v>7477</v>
       </c>
       <c r="C628" t="s">
         <v>1209</v>
@@ -30314,10 +30344,10 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B629" t="e">
-        <v>#N/A</v>
+        <v>1207</v>
+      </c>
+      <c r="B629">
+        <v>7478</v>
       </c>
       <c r="C629" t="s">
         <v>1209</v>
@@ -30325,10 +30355,10 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B630" t="e">
-        <v>#N/A</v>
+        <v>1646</v>
+      </c>
+      <c r="B630">
+        <v>7479</v>
       </c>
       <c r="C630" t="s">
         <v>1209</v>
@@ -30336,10 +30366,10 @@
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B631" t="e">
-        <v>#N/A</v>
+        <v>1208</v>
+      </c>
+      <c r="B631">
+        <v>1751</v>
       </c>
       <c r="C631" t="s">
         <v>1209</v>
@@ -30347,10 +30377,10 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B632" t="e">
-        <v>#N/A</v>
+        <v>1209</v>
+      </c>
+      <c r="B632">
+        <v>914</v>
       </c>
       <c r="C632" t="s">
         <v>1209</v>
@@ -30358,10 +30388,10 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B633" t="e">
-        <v>#N/A</v>
+        <v>1210</v>
+      </c>
+      <c r="B633">
+        <v>7504</v>
       </c>
       <c r="C633" t="s">
         <v>1209</v>
@@ -30369,10 +30399,10 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B634" t="e">
-        <v>#N/A</v>
+        <v>1211</v>
+      </c>
+      <c r="B634">
+        <v>1755</v>
       </c>
       <c r="C634" t="s">
         <v>1209</v>
@@ -30380,10 +30410,10 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B635" t="e">
-        <v>#N/A</v>
+        <v>1212</v>
+      </c>
+      <c r="B635">
+        <v>7475</v>
       </c>
       <c r="C635" t="s">
         <v>1209</v>
@@ -30391,98 +30421,98 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>1216</v>
-      </c>
-      <c r="B636" t="e">
-        <v>#N/A</v>
+        <v>1213</v>
+      </c>
+      <c r="B636">
+        <v>7785</v>
       </c>
       <c r="C636" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B637" t="e">
-        <v>#N/A</v>
+        <v>1214</v>
+      </c>
+      <c r="B637">
+        <v>7786</v>
       </c>
       <c r="C637" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>1218</v>
-      </c>
-      <c r="B638" t="e">
-        <v>#N/A</v>
+        <v>1647</v>
+      </c>
+      <c r="B638">
+        <v>7545</v>
       </c>
       <c r="C638" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B639" t="e">
-        <v>#N/A</v>
+        <v>1215</v>
+      </c>
+      <c r="B639">
+        <v>7482</v>
       </c>
       <c r="C639" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>1118</v>
+        <v>1216</v>
       </c>
       <c r="B640">
-        <v>1415</v>
+        <v>7004</v>
       </c>
       <c r="C640" t="s">
-        <v>1637</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>1119</v>
+        <v>1217</v>
       </c>
       <c r="B641">
-        <v>1416</v>
+        <v>6</v>
       </c>
       <c r="C641" t="s">
-        <v>1637</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>1120</v>
+        <v>1218</v>
       </c>
       <c r="B642">
-        <v>25</v>
+        <v>1851</v>
       </c>
       <c r="C642" t="s">
-        <v>1637</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="B643">
-        <v>7</v>
+        <v>918</v>
       </c>
       <c r="C643" t="s">
-        <v>1637</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B644">
-        <v>1641</v>
+        <v>1415</v>
       </c>
       <c r="C644" t="s">
         <v>1637</v>
@@ -30490,10 +30520,10 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B645">
-        <v>1637</v>
+        <v>1416</v>
       </c>
       <c r="C645" t="s">
         <v>1637</v>
@@ -30501,10 +30531,10 @@
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B646">
-        <v>814</v>
+        <v>25</v>
       </c>
       <c r="C646" t="s">
         <v>1637</v>
@@ -30512,10 +30542,10 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B647">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C647" t="s">
         <v>1637</v>
@@ -30523,10 +30553,10 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="B648">
-        <v>1636</v>
+        <v>1641</v>
       </c>
       <c r="C648" t="s">
         <v>1637</v>
@@ -30534,10 +30564,10 @@
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B649">
-        <v>1409</v>
+        <v>1637</v>
       </c>
       <c r="C649" t="s">
         <v>1637</v>
@@ -30545,54 +30575,54 @@
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>1220</v>
+        <v>1124</v>
       </c>
       <c r="B650">
-        <v>1497</v>
+        <v>814</v>
       </c>
       <c r="C650" t="s">
-        <v>1234</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>1169</v>
+        <v>1125</v>
       </c>
       <c r="B651">
-        <v>1498</v>
+        <v>24</v>
       </c>
       <c r="C651" t="s">
-        <v>1234</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>1221</v>
+        <v>1126</v>
       </c>
       <c r="B652">
-        <v>4866</v>
+        <v>1636</v>
       </c>
       <c r="C652" t="s">
-        <v>1234</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>1222</v>
+        <v>1127</v>
       </c>
       <c r="B653">
-        <v>4865</v>
+        <v>1409</v>
       </c>
       <c r="C653" t="s">
-        <v>1234</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B654">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C654" t="s">
         <v>1234</v>
@@ -30600,10 +30630,10 @@
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>1224</v>
+        <v>1169</v>
       </c>
       <c r="B655">
-        <v>484</v>
+        <v>1498</v>
       </c>
       <c r="C655" t="s">
         <v>1234</v>
@@ -30611,10 +30641,10 @@
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B656" t="e">
-        <v>#N/A</v>
+        <v>1221</v>
+      </c>
+      <c r="B656">
+        <v>4866</v>
       </c>
       <c r="C656" t="s">
         <v>1234</v>
@@ -30622,10 +30652,10 @@
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B657" t="e">
-        <v>#N/A</v>
+        <v>1222</v>
+      </c>
+      <c r="B657">
+        <v>4865</v>
       </c>
       <c r="C657" t="s">
         <v>1234</v>
@@ -30633,10 +30663,10 @@
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B658" t="e">
-        <v>#N/A</v>
+        <v>1223</v>
+      </c>
+      <c r="B658">
+        <v>1499</v>
       </c>
       <c r="C658" t="s">
         <v>1234</v>
@@ -30644,10 +30674,10 @@
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>1616</v>
-      </c>
-      <c r="B659" t="e">
-        <v>#N/A</v>
+        <v>1224</v>
+      </c>
+      <c r="B659">
+        <v>484</v>
       </c>
       <c r="C659" t="s">
         <v>1234</v>
@@ -30655,10 +30685,10 @@
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B660" t="e">
-        <v>#N/A</v>
+        <v>1225</v>
+      </c>
+      <c r="B660">
+        <v>4864</v>
       </c>
       <c r="C660" t="s">
         <v>1234</v>
@@ -30666,10 +30696,10 @@
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B661" t="e">
-        <v>#N/A</v>
+        <v>1226</v>
+      </c>
+      <c r="B661">
+        <v>4863</v>
       </c>
       <c r="C661" t="s">
         <v>1234</v>
@@ -30677,10 +30707,10 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>1617</v>
-      </c>
-      <c r="B662" t="e">
-        <v>#N/A</v>
+        <v>1227</v>
+      </c>
+      <c r="B662">
+        <v>1500</v>
       </c>
       <c r="C662" t="s">
         <v>1234</v>
@@ -30688,10 +30718,10 @@
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B663" t="e">
-        <v>#N/A</v>
+        <v>1616</v>
+      </c>
+      <c r="B663">
+        <v>502</v>
       </c>
       <c r="C663" t="s">
         <v>1234</v>
@@ -30699,10 +30729,10 @@
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>1618</v>
-      </c>
-      <c r="B664" t="e">
-        <v>#N/A</v>
+        <v>1228</v>
+      </c>
+      <c r="B664">
+        <v>1501</v>
       </c>
       <c r="C664" t="s">
         <v>1234</v>
@@ -30710,10 +30740,10 @@
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B665" t="e">
-        <v>#N/A</v>
+        <v>1229</v>
+      </c>
+      <c r="B665">
+        <v>6061</v>
       </c>
       <c r="C665" t="s">
         <v>1234</v>
@@ -30721,10 +30751,10 @@
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B666" t="e">
-        <v>#N/A</v>
+        <v>1617</v>
+      </c>
+      <c r="B666">
+        <v>490</v>
       </c>
       <c r="C666" t="s">
         <v>1234</v>
@@ -30732,10 +30762,10 @@
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B667" t="e">
-        <v>#N/A</v>
+        <v>1230</v>
+      </c>
+      <c r="B667">
+        <v>508</v>
       </c>
       <c r="C667" t="s">
         <v>1234</v>
@@ -30743,10 +30773,10 @@
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B668" t="e">
-        <v>#N/A</v>
+        <v>1618</v>
+      </c>
+      <c r="B668">
+        <v>512</v>
       </c>
       <c r="C668" t="s">
         <v>1234</v>
@@ -30754,10 +30784,10 @@
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>1619</v>
-      </c>
-      <c r="B669" t="e">
-        <v>#N/A</v>
+        <v>1231</v>
+      </c>
+      <c r="B669">
+        <v>516</v>
       </c>
       <c r="C669" t="s">
         <v>1234</v>
@@ -30765,10 +30795,10 @@
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B670" t="e">
-        <v>#N/A</v>
+        <v>1232</v>
+      </c>
+      <c r="B670">
+        <v>1502</v>
       </c>
       <c r="C670" t="s">
         <v>1234</v>
@@ -30776,461 +30806,461 @@
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B671" t="e">
-        <v>#N/A</v>
+        <v>1233</v>
+      </c>
+      <c r="B671">
+        <v>4856</v>
       </c>
       <c r="C671" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B672" t="e">
-        <v>#N/A</v>
+        <v>1234</v>
+      </c>
+      <c r="B672">
+        <v>518</v>
       </c>
       <c r="C672" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B673" t="e">
-        <v>#N/A</v>
+        <v>1619</v>
+      </c>
+      <c r="B673">
+        <v>7050</v>
       </c>
       <c r="C673" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B674" t="e">
-        <v>#N/A</v>
+        <v>1235</v>
+      </c>
+      <c r="B674">
+        <v>1503</v>
       </c>
       <c r="C674" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B675" t="e">
-        <v>#N/A</v>
+        <v>1236</v>
+      </c>
+      <c r="B675">
+        <v>2402</v>
       </c>
       <c r="C675" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B676" t="e">
-        <v>#N/A</v>
+        <v>1237</v>
+      </c>
+      <c r="B676">
+        <v>2051</v>
       </c>
       <c r="C676" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B677" t="e">
-        <v>#N/A</v>
+        <v>1238</v>
+      </c>
+      <c r="B677">
+        <v>929</v>
       </c>
       <c r="C677" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B678" t="e">
-        <v>#N/A</v>
+        <v>1638</v>
+      </c>
+      <c r="B678">
+        <v>2123</v>
       </c>
       <c r="C678" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B679" t="e">
-        <v>#N/A</v>
+        <v>1639</v>
+      </c>
+      <c r="B679">
+        <v>2199</v>
       </c>
       <c r="C679" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>1245</v>
-      </c>
-      <c r="B680" t="e">
-        <v>#N/A</v>
+        <v>1640</v>
+      </c>
+      <c r="B680">
+        <v>2229</v>
       </c>
       <c r="C680" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B681" t="e">
-        <v>#N/A</v>
+        <v>1641</v>
+      </c>
+      <c r="B681">
+        <v>2294</v>
       </c>
       <c r="C681" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B682" t="e">
-        <v>#N/A</v>
+        <v>1642</v>
+      </c>
+      <c r="B682">
+        <v>1979</v>
       </c>
       <c r="C682" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B683" t="e">
-        <v>#N/A</v>
+        <v>1239</v>
+      </c>
+      <c r="B683">
+        <v>2556</v>
       </c>
       <c r="C683" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B684" t="e">
-        <v>#N/A</v>
+        <v>1240</v>
+      </c>
+      <c r="B684">
+        <v>2553</v>
       </c>
       <c r="C684" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
       <c r="B685">
-        <v>140</v>
+        <v>2554</v>
       </c>
       <c r="C685" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>1251</v>
-      </c>
-      <c r="B686" t="e">
-        <v>#N/A</v>
+        <v>1242</v>
+      </c>
+      <c r="B686">
+        <v>172</v>
       </c>
       <c r="C686" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B687" t="e">
-        <v>#N/A</v>
+        <v>1243</v>
+      </c>
+      <c r="B687">
+        <v>2555</v>
       </c>
       <c r="C687" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B688" t="e">
-        <v>#N/A</v>
+        <v>1244</v>
+      </c>
+      <c r="B688">
+        <v>765</v>
       </c>
       <c r="C688" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B689" t="e">
-        <v>#N/A</v>
+        <v>1245</v>
+      </c>
+      <c r="B689">
+        <v>7594</v>
       </c>
       <c r="C689" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B690" t="e">
-        <v>#N/A</v>
+        <v>1246</v>
+      </c>
+      <c r="B690">
+        <v>9</v>
       </c>
       <c r="C690" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>1256</v>
+        <v>1247</v>
       </c>
       <c r="B691">
-        <v>3100</v>
+        <v>942</v>
       </c>
       <c r="C691" t="s">
-        <v>1260</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="B692">
-        <v>6539</v>
+        <v>2055</v>
       </c>
       <c r="C692" t="s">
-        <v>1260</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
       <c r="B693">
-        <v>709</v>
+        <v>941</v>
       </c>
       <c r="C693" t="s">
-        <v>1260</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>1259</v>
+        <v>1250</v>
       </c>
       <c r="B694">
-        <v>886</v>
+        <v>140</v>
       </c>
       <c r="C694" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>1260</v>
+        <v>1251</v>
       </c>
       <c r="B695">
-        <v>948</v>
+        <v>5639</v>
       </c>
       <c r="C695" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>1261</v>
+        <v>1252</v>
       </c>
       <c r="B696">
-        <v>1053</v>
+        <v>5640</v>
       </c>
       <c r="C696" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="B697">
-        <v>1086</v>
+        <v>419</v>
       </c>
       <c r="C697" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>1263</v>
+        <v>1254</v>
       </c>
       <c r="B698">
-        <v>5574</v>
+        <v>138</v>
       </c>
       <c r="C698" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="B699">
-        <v>892</v>
+        <v>5641</v>
       </c>
       <c r="C699" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>1265</v>
+        <v>1256</v>
       </c>
       <c r="B700">
-        <v>952</v>
+        <v>3100</v>
       </c>
       <c r="C700" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="B701">
-        <v>3575</v>
+        <v>6539</v>
       </c>
       <c r="C701" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>1267</v>
+        <v>1258</v>
       </c>
       <c r="B702">
-        <v>1018</v>
+        <v>709</v>
       </c>
       <c r="C702" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>1560</v>
+        <v>1259</v>
       </c>
       <c r="B703">
-        <v>8026</v>
+        <v>886</v>
       </c>
       <c r="C703" t="s">
-        <v>876</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>870</v>
+        <v>1260</v>
       </c>
       <c r="B704">
-        <v>2495</v>
+        <v>948</v>
       </c>
       <c r="C704" t="s">
-        <v>876</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>871</v>
+        <v>1261</v>
       </c>
       <c r="B705">
-        <v>3520</v>
+        <v>1053</v>
       </c>
       <c r="C705" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>872</v>
+        <v>1262</v>
       </c>
       <c r="B706">
-        <v>764</v>
+        <v>1086</v>
       </c>
       <c r="C706" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>873</v>
+        <v>1263</v>
       </c>
       <c r="B707">
-        <v>2035</v>
+        <v>5574</v>
       </c>
       <c r="C707" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>874</v>
+        <v>1264</v>
       </c>
       <c r="B708">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="C708" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>875</v>
+        <v>1265</v>
       </c>
       <c r="B709">
-        <v>1172</v>
+        <v>952</v>
       </c>
       <c r="C709" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>876</v>
+        <v>1266</v>
       </c>
       <c r="B710">
-        <v>962</v>
+        <v>3575</v>
       </c>
       <c r="C710" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>877</v>
+        <v>1267</v>
       </c>
       <c r="B711">
-        <v>2494</v>
+        <v>1018</v>
       </c>
       <c r="C711" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>878</v>
+        <v>1560</v>
       </c>
       <c r="B712">
-        <v>8025</v>
+        <v>8026</v>
       </c>
       <c r="C712" t="s">
         <v>876</v>
@@ -31238,10 +31268,10 @@
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B713">
-        <v>1015</v>
+        <v>2495</v>
       </c>
       <c r="C713" t="s">
         <v>876</v>
@@ -31249,274 +31279,274 @@
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>1268</v>
+        <v>871</v>
       </c>
       <c r="B714">
-        <v>310</v>
+        <v>3520</v>
       </c>
       <c r="C714" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>1269</v>
+        <v>872</v>
       </c>
       <c r="B715">
-        <v>321</v>
+        <v>764</v>
       </c>
       <c r="C715" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>1270</v>
+        <v>873</v>
       </c>
       <c r="B716">
-        <v>306</v>
+        <v>2035</v>
       </c>
       <c r="C716" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>1271</v>
+        <v>874</v>
       </c>
       <c r="B717">
-        <v>322</v>
+        <v>900</v>
       </c>
       <c r="C717" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>1272</v>
+        <v>875</v>
       </c>
       <c r="B718">
-        <v>311</v>
+        <v>1172</v>
       </c>
       <c r="C718" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>1273</v>
+        <v>876</v>
       </c>
       <c r="B719">
-        <v>2798</v>
+        <v>962</v>
       </c>
       <c r="C719" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>1274</v>
+        <v>877</v>
       </c>
       <c r="B720">
-        <v>12</v>
+        <v>2494</v>
       </c>
       <c r="C720" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>1275</v>
+        <v>878</v>
       </c>
       <c r="B721">
-        <v>2797</v>
+        <v>8025</v>
       </c>
       <c r="C721" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>1620</v>
+        <v>879</v>
       </c>
       <c r="B722">
-        <v>3977</v>
+        <v>1015</v>
       </c>
       <c r="C722" t="s">
-        <v>1276</v>
+        <v>876</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="B723">
-        <v>1998</v>
+        <v>310</v>
       </c>
       <c r="C723" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="B724">
-        <v>5905</v>
+        <v>321</v>
       </c>
       <c r="C724" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="B725">
-        <v>973</v>
+        <v>306</v>
       </c>
       <c r="C725" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>880</v>
+        <v>1271</v>
       </c>
       <c r="B726">
-        <v>6570</v>
+        <v>322</v>
       </c>
       <c r="C726" t="s">
-        <v>881</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>881</v>
-      </c>
-      <c r="B727" t="e">
-        <v>#N/A</v>
+        <v>1272</v>
+      </c>
+      <c r="B727">
+        <v>311</v>
       </c>
       <c r="C727" t="s">
-        <v>881</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>882</v>
-      </c>
-      <c r="B728" t="e">
-        <v>#N/A</v>
+        <v>1273</v>
+      </c>
+      <c r="B728">
+        <v>2798</v>
       </c>
       <c r="C728" t="s">
-        <v>881</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="B729">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C729" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="B730">
-        <v>52</v>
+        <v>2797</v>
       </c>
       <c r="C730" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>1281</v>
+        <v>1620</v>
       </c>
       <c r="B731">
-        <v>51</v>
+        <v>3977</v>
       </c>
       <c r="C731" t="s">
-        <v>1290</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="B732">
-        <v>1157</v>
+        <v>1998</v>
       </c>
       <c r="C732" t="s">
-        <v>1290</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="B733">
-        <v>2187</v>
+        <v>5905</v>
       </c>
       <c r="C733" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="B734">
-        <v>50</v>
+        <v>973</v>
       </c>
       <c r="C734" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>1285</v>
+        <v>880</v>
       </c>
       <c r="B735">
-        <v>33</v>
+        <v>6570</v>
       </c>
       <c r="C735" t="s">
-        <v>1290</v>
+        <v>881</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>1286</v>
+        <v>881</v>
       </c>
       <c r="B736">
-        <v>4225</v>
+        <v>3267</v>
       </c>
       <c r="C736" t="s">
-        <v>1290</v>
+        <v>881</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>1287</v>
+        <v>882</v>
       </c>
       <c r="B737">
-        <v>177</v>
+        <v>986</v>
       </c>
       <c r="C737" t="s">
-        <v>1290</v>
+        <v>881</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
       <c r="B738">
-        <v>1156</v>
+        <v>31</v>
       </c>
       <c r="C738" t="s">
         <v>1290</v>
@@ -31524,10 +31554,10 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>897</v>
+        <v>1280</v>
       </c>
       <c r="B739">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C739" t="s">
         <v>1290</v>
@@ -31535,10 +31565,10 @@
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="B740">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="C740" t="s">
         <v>1290</v>
@@ -31546,10 +31576,10 @@
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="B741">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="C741" t="s">
         <v>1290</v>
@@ -31557,10 +31587,10 @@
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="B742">
-        <v>46</v>
+        <v>2187</v>
       </c>
       <c r="C742" t="s">
         <v>1290</v>
@@ -31568,10 +31598,10 @@
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="B743">
-        <v>3578</v>
+        <v>50</v>
       </c>
       <c r="C743" t="s">
         <v>1290</v>
@@ -31579,142 +31609,142 @@
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="B744">
-        <v>2598</v>
+        <v>33</v>
       </c>
       <c r="C744" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="B745">
-        <v>3792</v>
+        <v>4225</v>
       </c>
       <c r="C745" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="B746">
-        <v>1938</v>
+        <v>177</v>
       </c>
       <c r="C746" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>1621</v>
+        <v>1288</v>
       </c>
       <c r="B747">
-        <v>6584</v>
+        <v>1156</v>
       </c>
       <c r="C747" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>1296</v>
+        <v>897</v>
       </c>
       <c r="B748">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C748" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="B749">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C749" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>1622</v>
+        <v>1290</v>
       </c>
       <c r="B750">
-        <v>6586</v>
+        <v>1</v>
       </c>
       <c r="C750" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
       <c r="B751">
-        <v>3412</v>
+        <v>46</v>
       </c>
       <c r="C751" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>1623</v>
+        <v>1292</v>
       </c>
       <c r="B752">
-        <v>6587</v>
+        <v>3578</v>
       </c>
       <c r="C752" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>1624</v>
+        <v>1293</v>
       </c>
       <c r="B753">
-        <v>6585</v>
+        <v>2598</v>
       </c>
       <c r="C753" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>1625</v>
+        <v>1294</v>
       </c>
       <c r="B754">
-        <v>39</v>
+        <v>3792</v>
       </c>
       <c r="C754" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="B755">
-        <v>38</v>
+        <v>1938</v>
       </c>
       <c r="C755" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="B756">
-        <v>41</v>
+        <v>6584</v>
       </c>
       <c r="C756" t="s">
         <v>1300</v>
@@ -31722,10 +31752,10 @@
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="B757">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C757" t="s">
         <v>1300</v>
@@ -31733,10 +31763,10 @@
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>1627</v>
+        <v>1297</v>
       </c>
       <c r="B758">
-        <v>6583</v>
+        <v>40</v>
       </c>
       <c r="C758" t="s">
         <v>1300</v>
@@ -31744,109 +31774,109 @@
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>1301</v>
+        <v>1622</v>
       </c>
       <c r="B759">
-        <v>403</v>
+        <v>6586</v>
       </c>
       <c r="C759" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="B760">
-        <v>4720</v>
+        <v>3412</v>
       </c>
       <c r="C760" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>705</v>
+        <v>1623</v>
       </c>
       <c r="B761">
-        <v>16</v>
+        <v>6587</v>
       </c>
       <c r="C761" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>1303</v>
+        <v>1624</v>
       </c>
       <c r="B762">
-        <v>4721</v>
+        <v>6585</v>
       </c>
       <c r="C762" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>1304</v>
+        <v>1625</v>
       </c>
       <c r="B763">
-        <v>462</v>
+        <v>39</v>
       </c>
       <c r="C763" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>1628</v>
+        <v>1299</v>
       </c>
       <c r="B764">
-        <v>399</v>
+        <v>38</v>
       </c>
       <c r="C764" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>1305</v>
+        <v>1626</v>
       </c>
       <c r="B765">
-        <v>4726</v>
+        <v>41</v>
       </c>
       <c r="C765" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="B766">
-        <v>6049</v>
+        <v>37</v>
       </c>
       <c r="C766" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>1307</v>
+        <v>1627</v>
       </c>
       <c r="B767">
-        <v>4731</v>
+        <v>6583</v>
       </c>
       <c r="C767" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
       <c r="B768">
-        <v>4744</v>
+        <v>403</v>
       </c>
       <c r="C768" t="s">
         <v>1630</v>
@@ -31854,10 +31884,10 @@
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="B769">
-        <v>4748</v>
+        <v>4720</v>
       </c>
       <c r="C769" t="s">
         <v>1630</v>
@@ -31865,10 +31895,10 @@
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>1310</v>
+        <v>705</v>
       </c>
       <c r="B770">
-        <v>468</v>
+        <v>16</v>
       </c>
       <c r="C770" t="s">
         <v>1630</v>
@@ -31876,10 +31906,10 @@
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="B771">
-        <v>401</v>
+        <v>4721</v>
       </c>
       <c r="C771" t="s">
         <v>1630</v>
@@ -31887,10 +31917,10 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="B772">
-        <v>15</v>
+        <v>462</v>
       </c>
       <c r="C772" t="s">
         <v>1630</v>
@@ -31898,18 +31928,117 @@
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>1313</v>
+        <v>1628</v>
       </c>
       <c r="B773">
-        <v>6050</v>
+        <v>399</v>
       </c>
       <c r="C773" t="s">
         <v>1630</v>
       </c>
     </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B774">
+        <v>4726</v>
+      </c>
+      <c r="C774" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B775">
+        <v>6049</v>
+      </c>
+      <c r="C775" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B776">
+        <v>4731</v>
+      </c>
+      <c r="C776" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B777">
+        <v>4744</v>
+      </c>
+      <c r="C777" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B778">
+        <v>4748</v>
+      </c>
+      <c r="C778" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B779">
+        <v>468</v>
+      </c>
+      <c r="C779" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B780">
+        <v>401</v>
+      </c>
+      <c r="C780" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B781">
+        <v>15</v>
+      </c>
+      <c r="C781" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B782">
+        <v>6050</v>
+      </c>
+      <c r="C782" t="s">
+        <v>1630</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C773">
-    <sortCondition ref="C2:C773"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C782">
+    <sortCondition ref="C2:C782"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/data/city_crosswalk.xlsx
+++ b/data/city_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robert\OneDrive\Desktop\Bobby\GitHub\Skyscrapers\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243FD9A1-E007-4BEF-A24C-78E26E4FC117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279D93DC-5786-40D5-B6F4-4FBDB499DEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{96C4E9D1-39CB-4160-B661-174130F89492}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Crosswalk" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Crosswalk!$A$1:$C$782</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Crosswalk!$A$1:$C$783</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
     <definedName name="IQ_CY">10000</definedName>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="1649">
   <si>
     <t>name_city</t>
   </si>
@@ -7114,6 +7114,9 @@
   </si>
   <si>
     <t>Yeoju</t>
+  </si>
+  <si>
+    <t>Hallandale Beach</t>
   </si>
 </sst>
 </file>
@@ -21411,15 +21414,90 @@
     </row>
   </sheetData>
   <mergeCells count="105">
-    <mergeCell ref="A947:D947"/>
-    <mergeCell ref="A952:D952"/>
-    <mergeCell ref="A966:D966"/>
-    <mergeCell ref="A896:D896"/>
-    <mergeCell ref="A903:D903"/>
-    <mergeCell ref="A912:D912"/>
-    <mergeCell ref="A922:D922"/>
-    <mergeCell ref="A926:D926"/>
-    <mergeCell ref="A930:D930"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A202:D202"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="A223:D223"/>
+    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A240:D240"/>
+    <mergeCell ref="A253:D253"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A186:D186"/>
+    <mergeCell ref="A198:D198"/>
+    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A314:D314"/>
+    <mergeCell ref="A327:D327"/>
+    <mergeCell ref="A332:D332"/>
+    <mergeCell ref="A338:D338"/>
+    <mergeCell ref="A342:D342"/>
+    <mergeCell ref="A262:D262"/>
+    <mergeCell ref="A266:D266"/>
+    <mergeCell ref="A271:D271"/>
+    <mergeCell ref="A275:D275"/>
+    <mergeCell ref="A286:D286"/>
+    <mergeCell ref="A290:D290"/>
+    <mergeCell ref="A394:D394"/>
+    <mergeCell ref="A399:D399"/>
+    <mergeCell ref="A404:D404"/>
+    <mergeCell ref="A410:D410"/>
+    <mergeCell ref="A416:D416"/>
+    <mergeCell ref="A442:D442"/>
+    <mergeCell ref="A347:D347"/>
+    <mergeCell ref="A360:D360"/>
+    <mergeCell ref="A366:D366"/>
+    <mergeCell ref="A373:D373"/>
+    <mergeCell ref="A378:D378"/>
+    <mergeCell ref="A382:D382"/>
+    <mergeCell ref="A514:D514"/>
+    <mergeCell ref="A518:D518"/>
+    <mergeCell ref="A525:D525"/>
+    <mergeCell ref="A531:D531"/>
+    <mergeCell ref="A552:D552"/>
+    <mergeCell ref="A556:D556"/>
+    <mergeCell ref="A446:D446"/>
+    <mergeCell ref="A451:D451"/>
+    <mergeCell ref="A466:D466"/>
+    <mergeCell ref="A470:D470"/>
+    <mergeCell ref="A478:D478"/>
+    <mergeCell ref="A493:D493"/>
+    <mergeCell ref="A617:D617"/>
+    <mergeCell ref="A625:D625"/>
+    <mergeCell ref="A629:D629"/>
+    <mergeCell ref="A683:D683"/>
+    <mergeCell ref="A695:D695"/>
+    <mergeCell ref="A702:D702"/>
+    <mergeCell ref="A561:D561"/>
+    <mergeCell ref="A566:D566"/>
+    <mergeCell ref="A570:D570"/>
+    <mergeCell ref="A601:D601"/>
+    <mergeCell ref="A605:D605"/>
+    <mergeCell ref="A612:D612"/>
+    <mergeCell ref="A740:D740"/>
+    <mergeCell ref="A744:D744"/>
+    <mergeCell ref="A748:D748"/>
+    <mergeCell ref="A752:D752"/>
+    <mergeCell ref="A756:D756"/>
+    <mergeCell ref="A769:D769"/>
+    <mergeCell ref="A710:D710"/>
+    <mergeCell ref="A714:D714"/>
+    <mergeCell ref="A718:D718"/>
+    <mergeCell ref="A726:D726"/>
+    <mergeCell ref="A730:D730"/>
+    <mergeCell ref="A736:D736"/>
     <mergeCell ref="A843:D843"/>
     <mergeCell ref="A866:D866"/>
     <mergeCell ref="A871:D871"/>
@@ -21432,90 +21510,15 @@
     <mergeCell ref="A808:D808"/>
     <mergeCell ref="A835:D835"/>
     <mergeCell ref="A839:D839"/>
-    <mergeCell ref="A740:D740"/>
-    <mergeCell ref="A744:D744"/>
-    <mergeCell ref="A748:D748"/>
-    <mergeCell ref="A752:D752"/>
-    <mergeCell ref="A756:D756"/>
-    <mergeCell ref="A769:D769"/>
-    <mergeCell ref="A710:D710"/>
-    <mergeCell ref="A714:D714"/>
-    <mergeCell ref="A718:D718"/>
-    <mergeCell ref="A726:D726"/>
-    <mergeCell ref="A730:D730"/>
-    <mergeCell ref="A736:D736"/>
-    <mergeCell ref="A617:D617"/>
-    <mergeCell ref="A625:D625"/>
-    <mergeCell ref="A629:D629"/>
-    <mergeCell ref="A683:D683"/>
-    <mergeCell ref="A695:D695"/>
-    <mergeCell ref="A702:D702"/>
-    <mergeCell ref="A561:D561"/>
-    <mergeCell ref="A566:D566"/>
-    <mergeCell ref="A570:D570"/>
-    <mergeCell ref="A601:D601"/>
-    <mergeCell ref="A605:D605"/>
-    <mergeCell ref="A612:D612"/>
-    <mergeCell ref="A514:D514"/>
-    <mergeCell ref="A518:D518"/>
-    <mergeCell ref="A525:D525"/>
-    <mergeCell ref="A531:D531"/>
-    <mergeCell ref="A552:D552"/>
-    <mergeCell ref="A556:D556"/>
-    <mergeCell ref="A446:D446"/>
-    <mergeCell ref="A451:D451"/>
-    <mergeCell ref="A466:D466"/>
-    <mergeCell ref="A470:D470"/>
-    <mergeCell ref="A478:D478"/>
-    <mergeCell ref="A493:D493"/>
-    <mergeCell ref="A394:D394"/>
-    <mergeCell ref="A399:D399"/>
-    <mergeCell ref="A404:D404"/>
-    <mergeCell ref="A410:D410"/>
-    <mergeCell ref="A416:D416"/>
-    <mergeCell ref="A442:D442"/>
-    <mergeCell ref="A347:D347"/>
-    <mergeCell ref="A360:D360"/>
-    <mergeCell ref="A366:D366"/>
-    <mergeCell ref="A373:D373"/>
-    <mergeCell ref="A378:D378"/>
-    <mergeCell ref="A382:D382"/>
-    <mergeCell ref="A310:D310"/>
-    <mergeCell ref="A314:D314"/>
-    <mergeCell ref="A327:D327"/>
-    <mergeCell ref="A332:D332"/>
-    <mergeCell ref="A338:D338"/>
-    <mergeCell ref="A342:D342"/>
-    <mergeCell ref="A262:D262"/>
-    <mergeCell ref="A266:D266"/>
-    <mergeCell ref="A271:D271"/>
-    <mergeCell ref="A275:D275"/>
-    <mergeCell ref="A286:D286"/>
-    <mergeCell ref="A290:D290"/>
-    <mergeCell ref="A202:D202"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A223:D223"/>
-    <mergeCell ref="A236:D236"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="A253:D253"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A175:D175"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A198:D198"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A947:D947"/>
+    <mergeCell ref="A952:D952"/>
+    <mergeCell ref="A966:D966"/>
+    <mergeCell ref="A896:D896"/>
+    <mergeCell ref="A903:D903"/>
+    <mergeCell ref="A912:D912"/>
+    <mergeCell ref="A922:D922"/>
+    <mergeCell ref="A926:D926"/>
+    <mergeCell ref="A930:D930"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://skyscraperpage.com/cities/?cityID=149" xr:uid="{DD369ABA-25BD-4D20-89A5-33EC39EDAA77}"/>
@@ -23426,7 +23429,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38210FFA-F41E-4694-9E11-07D3D8230991}">
-  <dimension ref="A1:C782"/>
+  <dimension ref="A1:C783"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -27605,10 +27608,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>988</v>
+        <v>1648</v>
       </c>
       <c r="B380">
-        <v>1097</v>
+        <v>2605</v>
       </c>
       <c r="C380" t="s">
         <v>991</v>
@@ -27616,10 +27619,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B381">
-        <v>4278</v>
+        <v>1097</v>
       </c>
       <c r="C381" t="s">
         <v>991</v>
@@ -27627,10 +27630,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B382">
-        <v>4277</v>
+        <v>4278</v>
       </c>
       <c r="C382" t="s">
         <v>991</v>
@@ -27638,10 +27641,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B383">
-        <v>134</v>
+        <v>4277</v>
       </c>
       <c r="C383" t="s">
         <v>991</v>
@@ -27649,10 +27652,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B384">
-        <v>417</v>
+        <v>134</v>
       </c>
       <c r="C384" t="s">
         <v>991</v>
@@ -27660,10 +27663,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B385">
-        <v>4270</v>
+        <v>417</v>
       </c>
       <c r="C385" t="s">
         <v>991</v>
@@ -27671,10 +27674,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B386">
-        <v>4269</v>
+        <v>4270</v>
       </c>
       <c r="C386" t="s">
         <v>991</v>
@@ -27682,10 +27685,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B387">
-        <v>4268</v>
+        <v>4269</v>
       </c>
       <c r="C387" t="s">
         <v>991</v>
@@ -27693,10 +27696,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B388">
-        <v>2738</v>
+        <v>4268</v>
       </c>
       <c r="C388" t="s">
         <v>991</v>
@@ -27704,10 +27707,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B389">
-        <v>2226</v>
+        <v>2738</v>
       </c>
       <c r="C389" t="s">
         <v>991</v>
@@ -27715,10 +27718,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B390">
-        <v>4263</v>
+        <v>2226</v>
       </c>
       <c r="C390" t="s">
         <v>991</v>
@@ -27726,10 +27729,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B391">
-        <v>1154</v>
+        <v>4263</v>
       </c>
       <c r="C391" t="s">
         <v>991</v>
@@ -27737,21 +27740,21 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B392">
-        <v>77</v>
+        <v>1154</v>
       </c>
       <c r="C392" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>1582</v>
+        <v>1000</v>
       </c>
       <c r="B393">
-        <v>3370</v>
+        <v>77</v>
       </c>
       <c r="C393" t="s">
         <v>1000</v>
@@ -27759,21 +27762,21 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>1001</v>
+        <v>1582</v>
       </c>
       <c r="B394">
-        <v>17</v>
+        <v>3370</v>
       </c>
       <c r="C394" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B395">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c r="C395" t="s">
         <v>1002</v>
@@ -27781,10 +27784,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B396">
-        <v>3909</v>
+        <v>255</v>
       </c>
       <c r="C396" t="s">
         <v>1002</v>
@@ -27792,10 +27795,10 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B397">
-        <v>258</v>
+        <v>3909</v>
       </c>
       <c r="C397" t="s">
         <v>1002</v>
@@ -27803,10 +27806,10 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B398">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C398" t="s">
         <v>1002</v>
@@ -27814,21 +27817,21 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B399">
-        <v>836</v>
+        <v>256</v>
       </c>
       <c r="C399" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B400">
-        <v>1977</v>
+        <v>836</v>
       </c>
       <c r="C400" t="s">
         <v>1006</v>
@@ -27836,10 +27839,10 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B401">
-        <v>904</v>
+        <v>1977</v>
       </c>
       <c r="C401" t="s">
         <v>1006</v>
@@ -27847,10 +27850,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B402">
-        <v>4221</v>
+        <v>904</v>
       </c>
       <c r="C402" t="s">
         <v>1006</v>
@@ -27858,21 +27861,21 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B403">
-        <v>7959</v>
+        <v>4221</v>
       </c>
       <c r="C403" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B404">
-        <v>4187</v>
+        <v>7959</v>
       </c>
       <c r="C404" t="s">
         <v>1018</v>
@@ -27880,10 +27883,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>1583</v>
+        <v>1011</v>
       </c>
       <c r="B405">
-        <v>8100</v>
+        <v>4187</v>
       </c>
       <c r="C405" t="s">
         <v>1018</v>
@@ -27891,10 +27894,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>1012</v>
+        <v>1583</v>
       </c>
       <c r="B406">
-        <v>7931</v>
+        <v>8100</v>
       </c>
       <c r="C406" t="s">
         <v>1018</v>
@@ -27902,10 +27905,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>1584</v>
+        <v>1012</v>
       </c>
       <c r="B407">
-        <v>7958</v>
+        <v>7931</v>
       </c>
       <c r="C407" t="s">
         <v>1018</v>
@@ -27913,10 +27916,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>1013</v>
+        <v>1584</v>
       </c>
       <c r="B408">
-        <v>7928</v>
+        <v>7958</v>
       </c>
       <c r="C408" t="s">
         <v>1018</v>
@@ -27924,10 +27927,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>1585</v>
+        <v>1013</v>
       </c>
       <c r="B409">
-        <v>6631</v>
+        <v>7928</v>
       </c>
       <c r="C409" t="s">
         <v>1018</v>
@@ -27935,10 +27938,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1014</v>
+        <v>1585</v>
       </c>
       <c r="B410">
-        <v>1060</v>
+        <v>6631</v>
       </c>
       <c r="C410" t="s">
         <v>1018</v>
@@ -27946,10 +27949,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B411">
-        <v>338</v>
+        <v>1060</v>
       </c>
       <c r="C411" t="s">
         <v>1018</v>
@@ -27957,10 +27960,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B412">
-        <v>7957</v>
+        <v>338</v>
       </c>
       <c r="C412" t="s">
         <v>1018</v>
@@ -27968,10 +27971,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B413">
-        <v>7956</v>
+        <v>7957</v>
       </c>
       <c r="C413" t="s">
         <v>1018</v>
@@ -27979,10 +27982,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B414">
-        <v>22</v>
+        <v>7956</v>
       </c>
       <c r="C414" t="s">
         <v>1018</v>
@@ -27990,10 +27993,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B415">
-        <v>7929</v>
+        <v>22</v>
       </c>
       <c r="C415" t="s">
         <v>1018</v>
@@ -28001,10 +28004,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B416">
-        <v>3583</v>
+        <v>7929</v>
       </c>
       <c r="C416" t="s">
         <v>1018</v>
@@ -28012,10 +28015,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B417">
-        <v>7926</v>
+        <v>3583</v>
       </c>
       <c r="C417" t="s">
         <v>1018</v>
@@ -28023,10 +28026,10 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B418">
-        <v>4188</v>
+        <v>7926</v>
       </c>
       <c r="C418" t="s">
         <v>1018</v>
@@ -28034,10 +28037,10 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B419">
-        <v>3397</v>
+        <v>4188</v>
       </c>
       <c r="C419" t="s">
         <v>1018</v>
@@ -28045,10 +28048,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B420">
-        <v>7955</v>
+        <v>3397</v>
       </c>
       <c r="C420" t="s">
         <v>1018</v>
@@ -28056,10 +28059,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B421">
-        <v>7932</v>
+        <v>7955</v>
       </c>
       <c r="C421" t="s">
         <v>1018</v>
@@ -28067,21 +28070,21 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B422">
-        <v>6762</v>
+        <v>7932</v>
       </c>
       <c r="C422" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B423">
-        <v>14</v>
+        <v>6762</v>
       </c>
       <c r="C423" t="s">
         <v>1027</v>
@@ -28089,21 +28092,21 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B424">
-        <v>839</v>
+        <v>14</v>
       </c>
       <c r="C424" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B425">
-        <v>3086</v>
+        <v>839</v>
       </c>
       <c r="C425" t="s">
         <v>1028</v>
@@ -28111,10 +28114,10 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B426">
-        <v>2166</v>
+        <v>3086</v>
       </c>
       <c r="C426" t="s">
         <v>1028</v>
@@ -28122,21 +28125,21 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B427">
-        <v>3416</v>
+        <v>2166</v>
       </c>
       <c r="C427" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B428">
-        <v>449</v>
+        <v>3416</v>
       </c>
       <c r="C428" t="s">
         <v>1035</v>
@@ -28144,21 +28147,21 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B429">
-        <v>273</v>
+        <v>449</v>
       </c>
       <c r="C429" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B430">
-        <v>4087</v>
+        <v>273</v>
       </c>
       <c r="C430" t="s">
         <v>1050</v>
@@ -28166,10 +28169,10 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B431">
-        <v>1342</v>
+        <v>4087</v>
       </c>
       <c r="C431" t="s">
         <v>1050</v>
@@ -28177,10 +28180,10 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B432">
-        <v>4089</v>
+        <v>1342</v>
       </c>
       <c r="C432" t="s">
         <v>1050</v>
@@ -28188,10 +28191,10 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B433">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="C433" t="s">
         <v>1050</v>
@@ -28199,10 +28202,10 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B434">
-        <v>1343</v>
+        <v>4090</v>
       </c>
       <c r="C434" t="s">
         <v>1050</v>
@@ -28210,10 +28213,10 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B435">
-        <v>266</v>
+        <v>1343</v>
       </c>
       <c r="C435" t="s">
         <v>1050</v>
@@ -28221,10 +28224,10 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B436">
-        <v>7232</v>
+        <v>266</v>
       </c>
       <c r="C436" t="s">
         <v>1050</v>
@@ -28232,10 +28235,10 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B437">
-        <v>272</v>
+        <v>7232</v>
       </c>
       <c r="C437" t="s">
         <v>1050</v>
@@ -28243,10 +28246,10 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B438">
-        <v>4070</v>
+        <v>272</v>
       </c>
       <c r="C438" t="s">
         <v>1050</v>
@@ -28254,10 +28257,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B439">
-        <v>1090</v>
+        <v>4070</v>
       </c>
       <c r="C439" t="s">
         <v>1050</v>
@@ -28265,10 +28268,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B440">
-        <v>158</v>
+        <v>1090</v>
       </c>
       <c r="C440" t="s">
         <v>1050</v>
@@ -28276,10 +28279,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>1586</v>
+        <v>1047</v>
       </c>
       <c r="B441">
-        <v>6672</v>
+        <v>158</v>
       </c>
       <c r="C441" t="s">
         <v>1050</v>
@@ -28287,10 +28290,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>1048</v>
+        <v>1586</v>
       </c>
       <c r="B442">
-        <v>1344</v>
+        <v>6672</v>
       </c>
       <c r="C442" t="s">
         <v>1050</v>
@@ -28298,10 +28301,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B443">
-        <v>2421</v>
+        <v>1344</v>
       </c>
       <c r="C443" t="s">
         <v>1050</v>
@@ -28309,10 +28312,10 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B444">
-        <v>8</v>
+        <v>2421</v>
       </c>
       <c r="C444" t="s">
         <v>1050</v>
@@ -28320,10 +28323,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B445">
-        <v>159</v>
+        <v>8</v>
       </c>
       <c r="C445" t="s">
         <v>1050</v>
@@ -28331,10 +28334,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B446">
-        <v>1345</v>
+        <v>159</v>
       </c>
       <c r="C446" t="s">
         <v>1050</v>
@@ -28342,10 +28345,10 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>1587</v>
+        <v>1052</v>
       </c>
       <c r="B447">
-        <v>6670</v>
+        <v>1345</v>
       </c>
       <c r="C447" t="s">
         <v>1050</v>
@@ -28353,10 +28356,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>1053</v>
+        <v>1587</v>
       </c>
       <c r="B448">
-        <v>275</v>
+        <v>6670</v>
       </c>
       <c r="C448" t="s">
         <v>1050</v>
@@ -28364,10 +28367,10 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>1588</v>
+        <v>1053</v>
       </c>
       <c r="B449">
-        <v>6671</v>
+        <v>275</v>
       </c>
       <c r="C449" t="s">
         <v>1050</v>
@@ -28375,10 +28378,10 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B450">
-        <v>4112</v>
+        <v>6671</v>
       </c>
       <c r="C450" t="s">
         <v>1050</v>
@@ -28386,10 +28389,10 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>1054</v>
+        <v>1589</v>
       </c>
       <c r="B451">
-        <v>4114</v>
+        <v>4112</v>
       </c>
       <c r="C451" t="s">
         <v>1050</v>
@@ -28397,10 +28400,10 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B452">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="C452" t="s">
         <v>1050</v>
@@ -28408,10 +28411,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B453">
-        <v>1687</v>
+        <v>4115</v>
       </c>
       <c r="C453" t="s">
         <v>1050</v>
@@ -28419,10 +28422,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B454">
-        <v>4120</v>
+        <v>1687</v>
       </c>
       <c r="C454" t="s">
         <v>1050</v>
@@ -28430,10 +28433,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B455">
-        <v>1347</v>
+        <v>4120</v>
       </c>
       <c r="C455" t="s">
         <v>1050</v>
@@ -28441,10 +28444,10 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B456">
-        <v>6970</v>
+        <v>1347</v>
       </c>
       <c r="C456" t="s">
         <v>1050</v>
@@ -28452,10 +28455,10 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B457">
-        <v>2222</v>
+        <v>6970</v>
       </c>
       <c r="C457" t="s">
         <v>1050</v>
@@ -28463,21 +28466,21 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B458">
-        <v>1123</v>
+        <v>2222</v>
       </c>
       <c r="C458" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B459">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="C459" t="s">
         <v>1062</v>
@@ -28485,21 +28488,21 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B460">
-        <v>88</v>
+        <v>1130</v>
       </c>
       <c r="C460" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B461">
-        <v>404</v>
+        <v>88</v>
       </c>
       <c r="C461" t="s">
         <v>1065</v>
@@ -28507,10 +28510,10 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B462">
-        <v>85</v>
+        <v>404</v>
       </c>
       <c r="C462" t="s">
         <v>1065</v>
@@ -28518,10 +28521,10 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B463">
-        <v>7474</v>
+        <v>85</v>
       </c>
       <c r="C463" t="s">
         <v>1065</v>
@@ -28529,10 +28532,10 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B464">
-        <v>86</v>
+        <v>7474</v>
       </c>
       <c r="C464" t="s">
         <v>1065</v>
@@ -28540,21 +28543,21 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B465">
-        <v>5452</v>
+        <v>86</v>
       </c>
       <c r="C465" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B466">
-        <v>5447</v>
+        <v>5452</v>
       </c>
       <c r="C466" t="s">
         <v>1070</v>
@@ -28562,10 +28565,10 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B467">
-        <v>139</v>
+        <v>5447</v>
       </c>
       <c r="C467" t="s">
         <v>1070</v>
@@ -28573,21 +28576,21 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B468">
-        <v>2541</v>
+        <v>139</v>
       </c>
       <c r="C468" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B469">
-        <v>2502</v>
+        <v>2541</v>
       </c>
       <c r="C469" t="s">
         <v>1074</v>
@@ -28595,10 +28598,10 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B470">
-        <v>773</v>
+        <v>2502</v>
       </c>
       <c r="C470" t="s">
         <v>1074</v>
@@ -28606,10 +28609,10 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B471">
-        <v>860</v>
+        <v>773</v>
       </c>
       <c r="C471" t="s">
         <v>1074</v>
@@ -28617,10 +28620,10 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B472">
-        <v>901</v>
+        <v>860</v>
       </c>
       <c r="C472" t="s">
         <v>1074</v>
@@ -28628,10 +28631,10 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B473">
-        <v>2559</v>
+        <v>901</v>
       </c>
       <c r="C473" t="s">
         <v>1074</v>
@@ -28639,21 +28642,21 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B474">
-        <v>64</v>
+        <v>2559</v>
       </c>
       <c r="C474" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B475">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C475" t="s">
         <v>1078</v>
@@ -28661,21 +28664,21 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B476">
-        <v>3813</v>
+        <v>60</v>
       </c>
       <c r="C476" t="s">
-        <v>1114</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>1590</v>
+        <v>1079</v>
       </c>
       <c r="B477">
-        <v>3798</v>
+        <v>3813</v>
       </c>
       <c r="C477" t="s">
         <v>1114</v>
@@ -28683,10 +28686,10 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>1080</v>
+        <v>1590</v>
       </c>
       <c r="B478">
-        <v>2333</v>
+        <v>3798</v>
       </c>
       <c r="C478" t="s">
         <v>1114</v>
@@ -28694,10 +28697,10 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B479">
-        <v>3820</v>
+        <v>2333</v>
       </c>
       <c r="C479" t="s">
         <v>1114</v>
@@ -28705,10 +28708,10 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>1591</v>
+        <v>1081</v>
       </c>
       <c r="B480">
-        <v>3830</v>
+        <v>3820</v>
       </c>
       <c r="C480" t="s">
         <v>1114</v>
@@ -28716,10 +28719,10 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>1082</v>
+        <v>1591</v>
       </c>
       <c r="B481">
-        <v>3806</v>
+        <v>3830</v>
       </c>
       <c r="C481" t="s">
         <v>1114</v>
@@ -28727,10 +28730,10 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B482">
-        <v>3797</v>
+        <v>3806</v>
       </c>
       <c r="C482" t="s">
         <v>1114</v>
@@ -28738,10 +28741,10 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B483">
-        <v>3805</v>
+        <v>3797</v>
       </c>
       <c r="C483" t="s">
         <v>1114</v>
@@ -28749,10 +28752,10 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B484">
-        <v>3801</v>
+        <v>3805</v>
       </c>
       <c r="C484" t="s">
         <v>1114</v>
@@ -28760,10 +28763,10 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B485">
-        <v>3818</v>
+        <v>3801</v>
       </c>
       <c r="C485" t="s">
         <v>1114</v>
@@ -28771,10 +28774,10 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B486">
-        <v>3392</v>
+        <v>3818</v>
       </c>
       <c r="C486" t="s">
         <v>1114</v>
@@ -28782,10 +28785,10 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B487">
-        <v>8036</v>
+        <v>3392</v>
       </c>
       <c r="C487" t="s">
         <v>1114</v>
@@ -28793,10 +28796,10 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>1592</v>
+        <v>1088</v>
       </c>
       <c r="B488">
-        <v>3817</v>
+        <v>8036</v>
       </c>
       <c r="C488" t="s">
         <v>1114</v>
@@ -28804,10 +28807,10 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>1089</v>
+        <v>1592</v>
       </c>
       <c r="B489">
-        <v>3804</v>
+        <v>3817</v>
       </c>
       <c r="C489" t="s">
         <v>1114</v>
@@ -28815,10 +28818,10 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B490">
-        <v>3448</v>
+        <v>3804</v>
       </c>
       <c r="C490" t="s">
         <v>1114</v>
@@ -28826,10 +28829,10 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B491">
-        <v>2328</v>
+        <v>3448</v>
       </c>
       <c r="C491" t="s">
         <v>1114</v>
@@ -28837,10 +28840,10 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B492">
-        <v>3800</v>
+        <v>2328</v>
       </c>
       <c r="C492" t="s">
         <v>1114</v>
@@ -28848,10 +28851,10 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B493">
-        <v>3823</v>
+        <v>3800</v>
       </c>
       <c r="C493" t="s">
         <v>1114</v>
@@ -28859,10 +28862,10 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B494">
-        <v>3808</v>
+        <v>3823</v>
       </c>
       <c r="C494" t="s">
         <v>1114</v>
@@ -28870,10 +28873,10 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B495">
-        <v>3829</v>
+        <v>3808</v>
       </c>
       <c r="C495" t="s">
         <v>1114</v>
@@ -28881,10 +28884,10 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B496">
-        <v>3809</v>
+        <v>3829</v>
       </c>
       <c r="C496" t="s">
         <v>1114</v>
@@ -28892,10 +28895,10 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B497">
-        <v>3648</v>
+        <v>3809</v>
       </c>
       <c r="C497" t="s">
         <v>1114</v>
@@ -28903,10 +28906,10 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B498">
-        <v>3819</v>
+        <v>3648</v>
       </c>
       <c r="C498" t="s">
         <v>1114</v>
@@ -28914,10 +28917,10 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B499">
-        <v>3825</v>
+        <v>3819</v>
       </c>
       <c r="C499" t="s">
         <v>1114</v>
@@ -28925,10 +28928,10 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B500">
-        <v>3828</v>
+        <v>3825</v>
       </c>
       <c r="C500" t="s">
         <v>1114</v>
@@ -28936,10 +28939,10 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B501">
-        <v>3647</v>
+        <v>3828</v>
       </c>
       <c r="C501" t="s">
         <v>1114</v>
@@ -28947,10 +28950,10 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B502">
-        <v>3374</v>
+        <v>3647</v>
       </c>
       <c r="C502" t="s">
         <v>1114</v>
@@ -28958,10 +28961,10 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="B503">
-        <v>3821</v>
+        <v>3374</v>
       </c>
       <c r="C503" t="s">
         <v>1114</v>
@@ -28969,10 +28972,10 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="B504">
-        <v>3807</v>
+        <v>3821</v>
       </c>
       <c r="C504" t="s">
         <v>1114</v>
@@ -28980,10 +28983,10 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B505">
-        <v>3814</v>
+        <v>3807</v>
       </c>
       <c r="C505" t="s">
         <v>1114</v>
@@ -28991,10 +28994,10 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B506">
-        <v>3810</v>
+        <v>3814</v>
       </c>
       <c r="C506" t="s">
         <v>1114</v>
@@ -29002,10 +29005,10 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B507">
-        <v>3816</v>
+        <v>3810</v>
       </c>
       <c r="C507" t="s">
         <v>1114</v>
@@ -29013,10 +29016,10 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B508">
-        <v>3386</v>
+        <v>3816</v>
       </c>
       <c r="C508" t="s">
         <v>1114</v>
@@ -29024,10 +29027,10 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>1593</v>
+        <v>1108</v>
       </c>
       <c r="B509">
-        <v>3827</v>
+        <v>3386</v>
       </c>
       <c r="C509" t="s">
         <v>1114</v>
@@ -29035,10 +29038,10 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>1109</v>
+        <v>1593</v>
       </c>
       <c r="B510">
-        <v>3799</v>
+        <v>3827</v>
       </c>
       <c r="C510" t="s">
         <v>1114</v>
@@ -29046,10 +29049,10 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B511">
-        <v>2330</v>
+        <v>3799</v>
       </c>
       <c r="C511" t="s">
         <v>1114</v>
@@ -29057,10 +29060,10 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B512">
-        <v>3802</v>
+        <v>2330</v>
       </c>
       <c r="C512" t="s">
         <v>1114</v>
@@ -29068,10 +29071,10 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B513">
-        <v>3815</v>
+        <v>3802</v>
       </c>
       <c r="C513" t="s">
         <v>1114</v>
@@ -29079,10 +29082,10 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>1594</v>
+        <v>1112</v>
       </c>
       <c r="B514">
-        <v>3824</v>
+        <v>3815</v>
       </c>
       <c r="C514" t="s">
         <v>1114</v>
@@ -29090,10 +29093,10 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>1113</v>
+        <v>1594</v>
       </c>
       <c r="B515">
-        <v>2064</v>
+        <v>3824</v>
       </c>
       <c r="C515" t="s">
         <v>1114</v>
@@ -29101,10 +29104,10 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B516">
-        <v>866</v>
+        <v>2064</v>
       </c>
       <c r="C516" t="s">
         <v>1114</v>
@@ -29112,10 +29115,10 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>1595</v>
+        <v>1114</v>
       </c>
       <c r="B517">
-        <v>2014</v>
+        <v>866</v>
       </c>
       <c r="C517" t="s">
         <v>1114</v>
@@ -29123,10 +29126,10 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>1115</v>
+        <v>1595</v>
       </c>
       <c r="B518">
-        <v>2329</v>
+        <v>2014</v>
       </c>
       <c r="C518" t="s">
         <v>1114</v>
@@ -29134,10 +29137,10 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B519">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="C519" t="s">
         <v>1114</v>
@@ -29145,10 +29148,10 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B520">
-        <v>3826</v>
+        <v>2332</v>
       </c>
       <c r="C520" t="s">
         <v>1114</v>
@@ -29156,10 +29159,10 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>1596</v>
+        <v>1117</v>
       </c>
       <c r="B521">
-        <v>4219</v>
+        <v>3826</v>
       </c>
       <c r="C521" t="s">
         <v>1114</v>
@@ -29167,10 +29170,10 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B522">
-        <v>3803</v>
+        <v>4219</v>
       </c>
       <c r="C522" t="s">
         <v>1114</v>
@@ -29178,10 +29181,10 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B523">
-        <v>4044</v>
+        <v>3803</v>
       </c>
       <c r="C523" t="s">
         <v>1114</v>
@@ -29189,10 +29192,10 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B524">
-        <v>3831</v>
+        <v>4044</v>
       </c>
       <c r="C524" t="s">
         <v>1114</v>
@@ -29200,10 +29203,10 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B525">
-        <v>3822</v>
+        <v>3831</v>
       </c>
       <c r="C525" t="s">
         <v>1114</v>
@@ -29211,10 +29214,10 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="B526">
-        <v>3811</v>
+        <v>3822</v>
       </c>
       <c r="C526" t="s">
         <v>1114</v>
@@ -29222,10 +29225,10 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B527">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="C527" t="s">
         <v>1114</v>
@@ -29233,21 +29236,21 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
-        <v>1128</v>
+        <v>1602</v>
       </c>
       <c r="B528">
-        <v>268</v>
+        <v>3812</v>
       </c>
       <c r="C528" t="s">
-        <v>1131</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B529">
-        <v>1341</v>
+        <v>268</v>
       </c>
       <c r="C529" t="s">
         <v>1131</v>
@@ -29255,10 +29258,10 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>1603</v>
+        <v>1129</v>
       </c>
       <c r="B530">
-        <v>3560</v>
+        <v>1341</v>
       </c>
       <c r="C530" t="s">
         <v>1131</v>
@@ -29266,10 +29269,10 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>1130</v>
+        <v>1603</v>
       </c>
       <c r="B531">
-        <v>1447</v>
+        <v>3560</v>
       </c>
       <c r="C531" t="s">
         <v>1131</v>
@@ -29277,10 +29280,10 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B532">
-        <v>326</v>
+        <v>1447</v>
       </c>
       <c r="C532" t="s">
         <v>1131</v>
@@ -29288,21 +29291,21 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>1604</v>
+        <v>1131</v>
       </c>
       <c r="B533">
-        <v>4185</v>
+        <v>326</v>
       </c>
       <c r="C533" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>824</v>
+        <v>1604</v>
       </c>
       <c r="B534">
-        <v>3156</v>
+        <v>4185</v>
       </c>
       <c r="C534" t="s">
         <v>1133</v>
@@ -29310,10 +29313,10 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>1132</v>
+        <v>824</v>
       </c>
       <c r="B535">
-        <v>165</v>
+        <v>3156</v>
       </c>
       <c r="C535" t="s">
         <v>1133</v>
@@ -29321,10 +29324,10 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B536">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C536" t="s">
         <v>1133</v>
@@ -29332,10 +29335,10 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B537">
-        <v>3157</v>
+        <v>164</v>
       </c>
       <c r="C537" t="s">
         <v>1133</v>
@@ -29343,10 +29346,10 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B538">
-        <v>2821</v>
+        <v>3157</v>
       </c>
       <c r="C538" t="s">
         <v>1133</v>
@@ -29354,21 +29357,21 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B539">
-        <v>6133</v>
+        <v>2821</v>
       </c>
       <c r="C539" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B540">
-        <v>327</v>
+        <v>6133</v>
       </c>
       <c r="C540" t="s">
         <v>1137</v>
@@ -29376,21 +29379,21 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>903</v>
+        <v>1137</v>
       </c>
       <c r="B541">
-        <v>6385</v>
+        <v>327</v>
       </c>
       <c r="C541" t="s">
-        <v>1634</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B542">
-        <v>6378</v>
+        <v>6385</v>
       </c>
       <c r="C542" t="s">
         <v>1634</v>
@@ -29398,10 +29401,10 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B543">
-        <v>755</v>
+        <v>6378</v>
       </c>
       <c r="C543" t="s">
         <v>1634</v>
@@ -29409,10 +29412,10 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B544">
-        <v>882</v>
+        <v>755</v>
       </c>
       <c r="C544" t="s">
         <v>1634</v>
@@ -29420,10 +29423,10 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B545">
-        <v>1349</v>
+        <v>882</v>
       </c>
       <c r="C545" t="s">
         <v>1634</v>
@@ -29431,10 +29434,10 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>1605</v>
+        <v>907</v>
       </c>
       <c r="B546">
-        <v>6610</v>
+        <v>1349</v>
       </c>
       <c r="C546" t="s">
         <v>1634</v>
@@ -29442,21 +29445,21 @@
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B547">
-        <v>5934</v>
+        <v>6610</v>
       </c>
       <c r="C547" t="s">
-        <v>1139</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>1138</v>
+        <v>1606</v>
       </c>
       <c r="B548">
-        <v>6879</v>
+        <v>5934</v>
       </c>
       <c r="C548" t="s">
         <v>1139</v>
@@ -29464,10 +29467,10 @@
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B549">
-        <v>1378</v>
+        <v>6879</v>
       </c>
       <c r="C549" t="s">
         <v>1139</v>
@@ -29475,10 +29478,10 @@
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B550">
-        <v>7655</v>
+        <v>1378</v>
       </c>
       <c r="C550" t="s">
         <v>1139</v>
@@ -29486,10 +29489,10 @@
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>1607</v>
+        <v>1140</v>
       </c>
       <c r="B551">
-        <v>4255</v>
+        <v>7655</v>
       </c>
       <c r="C551" t="s">
         <v>1139</v>
@@ -29497,10 +29500,10 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B552">
-        <v>3615</v>
+        <v>4255</v>
       </c>
       <c r="C552" t="s">
         <v>1139</v>
@@ -29508,21 +29511,21 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>1141</v>
+        <v>1608</v>
       </c>
       <c r="B553">
-        <v>3600</v>
+        <v>3615</v>
       </c>
       <c r="C553" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B554">
-        <v>2098</v>
+        <v>3600</v>
       </c>
       <c r="C554" t="s">
         <v>1142</v>
@@ -29530,21 +29533,21 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B555">
-        <v>7933</v>
+        <v>2098</v>
       </c>
       <c r="C555" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B556">
-        <v>6473</v>
+        <v>7933</v>
       </c>
       <c r="C556" t="s">
         <v>1145</v>
@@ -29552,10 +29555,10 @@
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B557">
-        <v>65</v>
+        <v>6473</v>
       </c>
       <c r="C557" t="s">
         <v>1145</v>
@@ -29563,10 +29566,10 @@
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B558">
-        <v>8105</v>
+        <v>65</v>
       </c>
       <c r="C558" t="s">
         <v>1145</v>
@@ -29574,21 +29577,21 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>1609</v>
+        <v>1146</v>
       </c>
       <c r="B559">
-        <v>2454</v>
+        <v>8105</v>
       </c>
       <c r="C559" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>1147</v>
+        <v>1609</v>
       </c>
       <c r="B560">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="C560" t="s">
         <v>1147</v>
@@ -29596,21 +29599,21 @@
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B561">
-        <v>3362</v>
+        <v>2453</v>
       </c>
       <c r="C561" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B562">
-        <v>7656</v>
+        <v>3362</v>
       </c>
       <c r="C562" t="s">
         <v>1148</v>
@@ -29618,21 +29621,21 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B563">
-        <v>162</v>
+        <v>7656</v>
       </c>
       <c r="C563" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B564">
-        <v>4237</v>
+        <v>162</v>
       </c>
       <c r="C564" t="s">
         <v>1150</v>
@@ -29640,21 +29643,21 @@
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B565">
-        <v>1211</v>
+        <v>4237</v>
       </c>
       <c r="C565" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B566">
-        <v>893</v>
+        <v>1211</v>
       </c>
       <c r="C566" t="s">
         <v>1153</v>
@@ -29662,21 +29665,21 @@
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B567">
-        <v>3901</v>
+        <v>893</v>
       </c>
       <c r="C567" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B568">
-        <v>3390</v>
+        <v>3901</v>
       </c>
       <c r="C568" t="s">
         <v>1155</v>
@@ -29684,21 +29687,21 @@
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B569">
-        <v>3426</v>
+        <v>3390</v>
       </c>
       <c r="C569" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B570">
-        <v>1092</v>
+        <v>3426</v>
       </c>
       <c r="C570" t="s">
         <v>1162</v>
@@ -29706,10 +29709,10 @@
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B571">
-        <v>1908</v>
+        <v>1092</v>
       </c>
       <c r="C571" t="s">
         <v>1162</v>
@@ -29717,10 +29720,10 @@
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B572">
-        <v>2609</v>
+        <v>1908</v>
       </c>
       <c r="C572" t="s">
         <v>1162</v>
@@ -29728,10 +29731,10 @@
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B573">
-        <v>1087</v>
+        <v>2609</v>
       </c>
       <c r="C573" t="s">
         <v>1162</v>
@@ -29739,10 +29742,10 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B574">
-        <v>1691</v>
+        <v>1087</v>
       </c>
       <c r="C574" t="s">
         <v>1162</v>
@@ -29750,10 +29753,10 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B575">
-        <v>897</v>
+        <v>1691</v>
       </c>
       <c r="C575" t="s">
         <v>1162</v>
@@ -29761,10 +29764,10 @@
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B576">
-        <v>2373</v>
+        <v>897</v>
       </c>
       <c r="C576" t="s">
         <v>1162</v>
@@ -29772,10 +29775,10 @@
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B577">
-        <v>1102</v>
+        <v>2373</v>
       </c>
       <c r="C577" t="s">
         <v>1162</v>
@@ -29783,10 +29786,10 @@
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B578">
-        <v>3610</v>
+        <v>1102</v>
       </c>
       <c r="C578" t="s">
         <v>1162</v>
@@ -29794,10 +29797,10 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>1610</v>
+        <v>1165</v>
       </c>
       <c r="B579">
-        <v>3436</v>
+        <v>3610</v>
       </c>
       <c r="C579" t="s">
         <v>1162</v>
@@ -29805,21 +29808,21 @@
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B580">
-        <v>392</v>
+        <v>3436</v>
       </c>
       <c r="C580" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>1166</v>
+        <v>1611</v>
       </c>
       <c r="B581">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C581" t="s">
         <v>1168</v>
@@ -29827,10 +29830,10 @@
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B582">
-        <v>91</v>
+        <v>397</v>
       </c>
       <c r="C582" t="s">
         <v>1168</v>
@@ -29838,10 +29841,10 @@
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B583">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C583" t="s">
         <v>1168</v>
@@ -29849,10 +29852,10 @@
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>1612</v>
+        <v>1168</v>
       </c>
       <c r="B584">
-        <v>6941</v>
+        <v>90</v>
       </c>
       <c r="C584" t="s">
         <v>1168</v>
@@ -29860,10 +29863,10 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B585">
-        <v>391</v>
+        <v>6941</v>
       </c>
       <c r="C585" t="s">
         <v>1168</v>
@@ -29871,21 +29874,21 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>1169</v>
+        <v>1613</v>
       </c>
       <c r="B586">
-        <v>209</v>
+        <v>391</v>
       </c>
       <c r="C586" t="s">
-        <v>1644</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B587">
-        <v>5029</v>
+        <v>209</v>
       </c>
       <c r="C587" t="s">
         <v>1644</v>
@@ -29893,10 +29896,10 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B588">
-        <v>6055</v>
+        <v>5029</v>
       </c>
       <c r="C588" t="s">
         <v>1644</v>
@@ -29904,10 +29907,10 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B589">
-        <v>5025</v>
+        <v>6055</v>
       </c>
       <c r="C589" t="s">
         <v>1644</v>
@@ -29915,10 +29918,10 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>1614</v>
+        <v>1172</v>
       </c>
       <c r="B590">
-        <v>6058</v>
+        <v>5025</v>
       </c>
       <c r="C590" t="s">
         <v>1644</v>
@@ -29926,10 +29929,10 @@
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>1173</v>
+        <v>1614</v>
       </c>
       <c r="B591">
-        <v>5018</v>
+        <v>6058</v>
       </c>
       <c r="C591" t="s">
         <v>1644</v>
@@ -29937,10 +29940,10 @@
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B592">
-        <v>113</v>
+        <v>5018</v>
       </c>
       <c r="C592" t="s">
         <v>1644</v>
@@ -29948,10 +29951,10 @@
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B593">
-        <v>3836</v>
+        <v>113</v>
       </c>
       <c r="C593" t="s">
         <v>1644</v>
@@ -29959,10 +29962,10 @@
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>897</v>
+        <v>1175</v>
       </c>
       <c r="B594">
-        <v>128</v>
+        <v>3836</v>
       </c>
       <c r="C594" t="s">
         <v>1644</v>
@@ -29970,10 +29973,10 @@
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>1176</v>
+        <v>897</v>
       </c>
       <c r="B595">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C595" t="s">
         <v>1644</v>
@@ -29981,10 +29984,10 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B596">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C596" t="s">
         <v>1644</v>
@@ -29992,10 +29995,10 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B597">
-        <v>5017</v>
+        <v>123</v>
       </c>
       <c r="C597" t="s">
         <v>1644</v>
@@ -30003,10 +30006,10 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B598">
-        <v>3414</v>
+        <v>5017</v>
       </c>
       <c r="C598" t="s">
         <v>1644</v>
@@ -30014,10 +30017,10 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B599">
-        <v>5014</v>
+        <v>3414</v>
       </c>
       <c r="C599" t="s">
         <v>1644</v>
@@ -30025,10 +30028,10 @@
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>1643</v>
+        <v>1180</v>
       </c>
       <c r="B600">
-        <v>124</v>
+        <v>5014</v>
       </c>
       <c r="C600" t="s">
         <v>1644</v>
@@ -30036,10 +30039,10 @@
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>1181</v>
+        <v>1643</v>
       </c>
       <c r="B601">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="C601" t="s">
         <v>1644</v>
@@ -30047,10 +30050,10 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B602">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C602" t="s">
         <v>1644</v>
@@ -30058,21 +30061,21 @@
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B603">
-        <v>2224</v>
+        <v>220</v>
       </c>
       <c r="C603" t="s">
-        <v>1184</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B604">
-        <v>909</v>
+        <v>2224</v>
       </c>
       <c r="C604" t="s">
         <v>1184</v>
@@ -30080,21 +30083,21 @@
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B605">
-        <v>83</v>
+        <v>909</v>
       </c>
       <c r="C605" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B606">
-        <v>1331</v>
+        <v>83</v>
       </c>
       <c r="C606" t="s">
         <v>1189</v>
@@ -30102,10 +30105,10 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>1615</v>
+        <v>1186</v>
       </c>
       <c r="B607">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C607" t="s">
         <v>1189</v>
@@ -30113,10 +30116,10 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>1187</v>
+        <v>1615</v>
       </c>
       <c r="B608">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="C608" t="s">
         <v>1189</v>
@@ -30124,10 +30127,10 @@
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B609">
-        <v>406</v>
+        <v>1327</v>
       </c>
       <c r="C609" t="s">
         <v>1189</v>
@@ -30135,10 +30138,10 @@
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B610">
-        <v>27</v>
+        <v>406</v>
       </c>
       <c r="C610" t="s">
         <v>1189</v>
@@ -30146,10 +30149,10 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B611">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C611" t="s">
         <v>1189</v>
@@ -30157,21 +30160,21 @@
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B612">
-        <v>7503</v>
+        <v>79</v>
       </c>
       <c r="C612" t="s">
-        <v>1209</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B613">
-        <v>8737</v>
+        <v>7503</v>
       </c>
       <c r="C613" t="s">
         <v>1209</v>
@@ -30179,10 +30182,10 @@
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B614">
-        <v>2833</v>
+        <v>8737</v>
       </c>
       <c r="C614" t="s">
         <v>1209</v>
@@ -30190,10 +30193,10 @@
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B615">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="C615" t="s">
         <v>1209</v>
@@ -30201,10 +30204,10 @@
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B616">
-        <v>1749</v>
+        <v>2836</v>
       </c>
       <c r="C616" t="s">
         <v>1209</v>
@@ -30212,10 +30215,10 @@
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B617">
-        <v>7505</v>
+        <v>1749</v>
       </c>
       <c r="C617" t="s">
         <v>1209</v>
@@ -30223,10 +30226,10 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B618">
-        <v>1759</v>
+        <v>7505</v>
       </c>
       <c r="C618" t="s">
         <v>1209</v>
@@ -30234,10 +30237,10 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B619">
-        <v>2834</v>
+        <v>1759</v>
       </c>
       <c r="C619" t="s">
         <v>1209</v>
@@ -30245,10 +30248,10 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B620">
-        <v>7476</v>
+        <v>2834</v>
       </c>
       <c r="C620" t="s">
         <v>1209</v>
@@ -30256,10 +30259,10 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B621">
-        <v>1765</v>
+        <v>7476</v>
       </c>
       <c r="C621" t="s">
         <v>1209</v>
@@ -30267,10 +30270,10 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B622">
-        <v>7480</v>
+        <v>1765</v>
       </c>
       <c r="C622" t="s">
         <v>1209</v>
@@ -30278,10 +30281,10 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B623">
-        <v>7481</v>
+        <v>7480</v>
       </c>
       <c r="C623" t="s">
         <v>1209</v>
@@ -30289,10 +30292,10 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B624">
-        <v>5488</v>
+        <v>7481</v>
       </c>
       <c r="C624" t="s">
         <v>1209</v>
@@ -30300,10 +30303,10 @@
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B625">
-        <v>6646</v>
+        <v>5488</v>
       </c>
       <c r="C625" t="s">
         <v>1209</v>
@@ -30311,10 +30314,10 @@
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B626">
-        <v>1756</v>
+        <v>6646</v>
       </c>
       <c r="C626" t="s">
         <v>1209</v>
@@ -30322,10 +30325,10 @@
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B627">
-        <v>5511</v>
+        <v>1756</v>
       </c>
       <c r="C627" t="s">
         <v>1209</v>
@@ -30333,10 +30336,10 @@
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>1645</v>
+        <v>1206</v>
       </c>
       <c r="B628">
-        <v>7477</v>
+        <v>5511</v>
       </c>
       <c r="C628" t="s">
         <v>1209</v>
@@ -30344,10 +30347,10 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>1207</v>
+        <v>1645</v>
       </c>
       <c r="B629">
-        <v>7478</v>
+        <v>7477</v>
       </c>
       <c r="C629" t="s">
         <v>1209</v>
@@ -30355,10 +30358,10 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>1646</v>
+        <v>1207</v>
       </c>
       <c r="B630">
-        <v>7479</v>
+        <v>7478</v>
       </c>
       <c r="C630" t="s">
         <v>1209</v>
@@ -30366,10 +30369,10 @@
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>1208</v>
+        <v>1646</v>
       </c>
       <c r="B631">
-        <v>1751</v>
+        <v>7479</v>
       </c>
       <c r="C631" t="s">
         <v>1209</v>
@@ -30377,10 +30380,10 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B632">
-        <v>914</v>
+        <v>1751</v>
       </c>
       <c r="C632" t="s">
         <v>1209</v>
@@ -30388,10 +30391,10 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B633">
-        <v>7504</v>
+        <v>914</v>
       </c>
       <c r="C633" t="s">
         <v>1209</v>
@@ -30399,10 +30402,10 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B634">
-        <v>1755</v>
+        <v>7504</v>
       </c>
       <c r="C634" t="s">
         <v>1209</v>
@@ -30410,10 +30413,10 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B635">
-        <v>7475</v>
+        <v>1755</v>
       </c>
       <c r="C635" t="s">
         <v>1209</v>
@@ -30421,10 +30424,10 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B636">
-        <v>7785</v>
+        <v>7475</v>
       </c>
       <c r="C636" t="s">
         <v>1209</v>
@@ -30432,10 +30435,10 @@
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B637">
-        <v>7786</v>
+        <v>7785</v>
       </c>
       <c r="C637" t="s">
         <v>1209</v>
@@ -30443,10 +30446,10 @@
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>1647</v>
+        <v>1214</v>
       </c>
       <c r="B638">
-        <v>7545</v>
+        <v>7786</v>
       </c>
       <c r="C638" t="s">
         <v>1209</v>
@@ -30454,10 +30457,10 @@
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>1215</v>
+        <v>1647</v>
       </c>
       <c r="B639">
-        <v>7482</v>
+        <v>7545</v>
       </c>
       <c r="C639" t="s">
         <v>1209</v>
@@ -30465,21 +30468,21 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B640">
-        <v>7004</v>
+        <v>7482</v>
       </c>
       <c r="C640" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B641">
-        <v>6</v>
+        <v>7004</v>
       </c>
       <c r="C641" t="s">
         <v>1217</v>
@@ -30487,21 +30490,21 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B642">
-        <v>1851</v>
+        <v>6</v>
       </c>
       <c r="C642" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B643">
-        <v>918</v>
+        <v>1851</v>
       </c>
       <c r="C643" t="s">
         <v>1219</v>
@@ -30509,21 +30512,21 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>1118</v>
+        <v>1219</v>
       </c>
       <c r="B644">
-        <v>1415</v>
+        <v>918</v>
       </c>
       <c r="C644" t="s">
-        <v>1637</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B645">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C645" t="s">
         <v>1637</v>
@@ -30531,10 +30534,10 @@
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B646">
-        <v>25</v>
+        <v>1416</v>
       </c>
       <c r="C646" t="s">
         <v>1637</v>
@@ -30542,10 +30545,10 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B647">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C647" t="s">
         <v>1637</v>
@@ -30553,10 +30556,10 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B648">
-        <v>1641</v>
+        <v>7</v>
       </c>
       <c r="C648" t="s">
         <v>1637</v>
@@ -30564,10 +30567,10 @@
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B649">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="C649" t="s">
         <v>1637</v>
@@ -30575,10 +30578,10 @@
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B650">
-        <v>814</v>
+        <v>1637</v>
       </c>
       <c r="C650" t="s">
         <v>1637</v>
@@ -30586,10 +30589,10 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B651">
-        <v>24</v>
+        <v>814</v>
       </c>
       <c r="C651" t="s">
         <v>1637</v>
@@ -30597,10 +30600,10 @@
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B652">
-        <v>1636</v>
+        <v>24</v>
       </c>
       <c r="C652" t="s">
         <v>1637</v>
@@ -30608,10 +30611,10 @@
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B653">
-        <v>1409</v>
+        <v>1636</v>
       </c>
       <c r="C653" t="s">
         <v>1637</v>
@@ -30619,21 +30622,21 @@
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>1220</v>
+        <v>1127</v>
       </c>
       <c r="B654">
-        <v>1497</v>
+        <v>1409</v>
       </c>
       <c r="C654" t="s">
-        <v>1234</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>1169</v>
+        <v>1220</v>
       </c>
       <c r="B655">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C655" t="s">
         <v>1234</v>
@@ -30641,10 +30644,10 @@
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>1221</v>
+        <v>1169</v>
       </c>
       <c r="B656">
-        <v>4866</v>
+        <v>1498</v>
       </c>
       <c r="C656" t="s">
         <v>1234</v>
@@ -30652,10 +30655,10 @@
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B657">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="C657" t="s">
         <v>1234</v>
@@ -30663,10 +30666,10 @@
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B658">
-        <v>1499</v>
+        <v>4865</v>
       </c>
       <c r="C658" t="s">
         <v>1234</v>
@@ -30674,10 +30677,10 @@
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B659">
-        <v>484</v>
+        <v>1499</v>
       </c>
       <c r="C659" t="s">
         <v>1234</v>
@@ -30685,10 +30688,10 @@
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B660">
-        <v>4864</v>
+        <v>484</v>
       </c>
       <c r="C660" t="s">
         <v>1234</v>
@@ -30696,10 +30699,10 @@
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B661">
-        <v>4863</v>
+        <v>4864</v>
       </c>
       <c r="C661" t="s">
         <v>1234</v>
@@ -30707,10 +30710,10 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B662">
-        <v>1500</v>
+        <v>4863</v>
       </c>
       <c r="C662" t="s">
         <v>1234</v>
@@ -30718,10 +30721,10 @@
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>1616</v>
+        <v>1227</v>
       </c>
       <c r="B663">
-        <v>502</v>
+        <v>1500</v>
       </c>
       <c r="C663" t="s">
         <v>1234</v>
@@ -30729,10 +30732,10 @@
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>1228</v>
+        <v>1616</v>
       </c>
       <c r="B664">
-        <v>1501</v>
+        <v>502</v>
       </c>
       <c r="C664" t="s">
         <v>1234</v>
@@ -30740,10 +30743,10 @@
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B665">
-        <v>6061</v>
+        <v>1501</v>
       </c>
       <c r="C665" t="s">
         <v>1234</v>
@@ -30751,10 +30754,10 @@
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>1617</v>
+        <v>1229</v>
       </c>
       <c r="B666">
-        <v>490</v>
+        <v>6061</v>
       </c>
       <c r="C666" t="s">
         <v>1234</v>
@@ -30762,10 +30765,10 @@
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>1230</v>
+        <v>1617</v>
       </c>
       <c r="B667">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="C667" t="s">
         <v>1234</v>
@@ -30773,10 +30776,10 @@
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>1618</v>
+        <v>1230</v>
       </c>
       <c r="B668">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C668" t="s">
         <v>1234</v>
@@ -30784,10 +30787,10 @@
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>1231</v>
+        <v>1618</v>
       </c>
       <c r="B669">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C669" t="s">
         <v>1234</v>
@@ -30795,10 +30798,10 @@
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B670">
-        <v>1502</v>
+        <v>516</v>
       </c>
       <c r="C670" t="s">
         <v>1234</v>
@@ -30806,10 +30809,10 @@
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B671">
-        <v>4856</v>
+        <v>1502</v>
       </c>
       <c r="C671" t="s">
         <v>1234</v>
@@ -30817,10 +30820,10 @@
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B672">
-        <v>518</v>
+        <v>4856</v>
       </c>
       <c r="C672" t="s">
         <v>1234</v>
@@ -30828,10 +30831,10 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>1619</v>
+        <v>1234</v>
       </c>
       <c r="B673">
-        <v>7050</v>
+        <v>518</v>
       </c>
       <c r="C673" t="s">
         <v>1234</v>
@@ -30839,10 +30842,10 @@
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>1235</v>
+        <v>1619</v>
       </c>
       <c r="B674">
-        <v>1503</v>
+        <v>7050</v>
       </c>
       <c r="C674" t="s">
         <v>1234</v>
@@ -30850,21 +30853,21 @@
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B675">
-        <v>2402</v>
+        <v>1503</v>
       </c>
       <c r="C675" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B676">
-        <v>2051</v>
+        <v>2402</v>
       </c>
       <c r="C676" t="s">
         <v>1238</v>
@@ -30872,10 +30875,10 @@
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B677">
-        <v>929</v>
+        <v>2051</v>
       </c>
       <c r="C677" t="s">
         <v>1238</v>
@@ -30883,10 +30886,10 @@
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>1638</v>
+        <v>1238</v>
       </c>
       <c r="B678">
-        <v>2123</v>
+        <v>929</v>
       </c>
       <c r="C678" t="s">
         <v>1238</v>
@@ -30894,10 +30897,10 @@
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B679">
-        <v>2199</v>
+        <v>2123</v>
       </c>
       <c r="C679" t="s">
         <v>1238</v>
@@ -30905,10 +30908,10 @@
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B680">
-        <v>2229</v>
+        <v>2199</v>
       </c>
       <c r="C680" t="s">
         <v>1238</v>
@@ -30916,10 +30919,10 @@
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B681">
-        <v>2294</v>
+        <v>2229</v>
       </c>
       <c r="C681" t="s">
         <v>1238</v>
@@ -30927,10 +30930,10 @@
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B682">
-        <v>1979</v>
+        <v>2294</v>
       </c>
       <c r="C682" t="s">
         <v>1238</v>
@@ -30938,21 +30941,21 @@
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>1239</v>
+        <v>1642</v>
       </c>
       <c r="B683">
-        <v>2556</v>
+        <v>1979</v>
       </c>
       <c r="C683" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B684">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="C684" t="s">
         <v>1242</v>
@@ -30960,10 +30963,10 @@
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B685">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="C685" t="s">
         <v>1242</v>
@@ -30971,10 +30974,10 @@
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B686">
-        <v>172</v>
+        <v>2554</v>
       </c>
       <c r="C686" t="s">
         <v>1242</v>
@@ -30982,10 +30985,10 @@
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B687">
-        <v>2555</v>
+        <v>172</v>
       </c>
       <c r="C687" t="s">
         <v>1242</v>
@@ -30993,21 +30996,21 @@
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B688">
-        <v>765</v>
+        <v>2555</v>
       </c>
       <c r="C688" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B689">
-        <v>7594</v>
+        <v>765</v>
       </c>
       <c r="C689" t="s">
         <v>1246</v>
@@ -31015,10 +31018,10 @@
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B690">
-        <v>9</v>
+        <v>7594</v>
       </c>
       <c r="C690" t="s">
         <v>1246</v>
@@ -31026,10 +31029,10 @@
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B691">
-        <v>942</v>
+        <v>9</v>
       </c>
       <c r="C691" t="s">
         <v>1246</v>
@@ -31037,21 +31040,21 @@
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B692">
-        <v>2055</v>
+        <v>942</v>
       </c>
       <c r="C692" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B693">
-        <v>941</v>
+        <v>2055</v>
       </c>
       <c r="C693" t="s">
         <v>1249</v>
@@ -31059,21 +31062,21 @@
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B694">
-        <v>140</v>
+        <v>941</v>
       </c>
       <c r="C694" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B695">
-        <v>5639</v>
+        <v>140</v>
       </c>
       <c r="C695" t="s">
         <v>1254</v>
@@ -31081,10 +31084,10 @@
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B696">
-        <v>5640</v>
+        <v>5639</v>
       </c>
       <c r="C696" t="s">
         <v>1254</v>
@@ -31092,10 +31095,10 @@
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B697">
-        <v>419</v>
+        <v>5640</v>
       </c>
       <c r="C697" t="s">
         <v>1254</v>
@@ -31103,10 +31106,10 @@
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B698">
-        <v>138</v>
+        <v>419</v>
       </c>
       <c r="C698" t="s">
         <v>1254</v>
@@ -31114,10 +31117,10 @@
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B699">
-        <v>5641</v>
+        <v>138</v>
       </c>
       <c r="C699" t="s">
         <v>1254</v>
@@ -31125,21 +31128,21 @@
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B700">
-        <v>3100</v>
+        <v>5641</v>
       </c>
       <c r="C700" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B701">
-        <v>6539</v>
+        <v>3100</v>
       </c>
       <c r="C701" t="s">
         <v>1260</v>
@@ -31147,10 +31150,10 @@
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B702">
-        <v>709</v>
+        <v>6539</v>
       </c>
       <c r="C702" t="s">
         <v>1260</v>
@@ -31158,10 +31161,10 @@
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B703">
-        <v>886</v>
+        <v>709</v>
       </c>
       <c r="C703" t="s">
         <v>1260</v>
@@ -31169,10 +31172,10 @@
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B704">
-        <v>948</v>
+        <v>886</v>
       </c>
       <c r="C704" t="s">
         <v>1260</v>
@@ -31180,21 +31183,21 @@
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B705">
-        <v>1053</v>
+        <v>948</v>
       </c>
       <c r="C705" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B706">
-        <v>1086</v>
+        <v>1053</v>
       </c>
       <c r="C706" t="s">
         <v>1265</v>
@@ -31202,10 +31205,10 @@
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B707">
-        <v>5574</v>
+        <v>1086</v>
       </c>
       <c r="C707" t="s">
         <v>1265</v>
@@ -31213,10 +31216,10 @@
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B708">
-        <v>892</v>
+        <v>5574</v>
       </c>
       <c r="C708" t="s">
         <v>1265</v>
@@ -31224,10 +31227,10 @@
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B709">
-        <v>952</v>
+        <v>892</v>
       </c>
       <c r="C709" t="s">
         <v>1265</v>
@@ -31235,10 +31238,10 @@
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B710">
-        <v>3575</v>
+        <v>952</v>
       </c>
       <c r="C710" t="s">
         <v>1265</v>
@@ -31246,10 +31249,10 @@
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B711">
-        <v>1018</v>
+        <v>3575</v>
       </c>
       <c r="C711" t="s">
         <v>1265</v>
@@ -31257,21 +31260,21 @@
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>1560</v>
+        <v>1267</v>
       </c>
       <c r="B712">
-        <v>8026</v>
+        <v>1018</v>
       </c>
       <c r="C712" t="s">
-        <v>876</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>870</v>
+        <v>1560</v>
       </c>
       <c r="B713">
-        <v>2495</v>
+        <v>8026</v>
       </c>
       <c r="C713" t="s">
         <v>876</v>
@@ -31279,10 +31282,10 @@
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B714">
-        <v>3520</v>
+        <v>2495</v>
       </c>
       <c r="C714" t="s">
         <v>876</v>
@@ -31290,10 +31293,10 @@
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B715">
-        <v>764</v>
+        <v>3520</v>
       </c>
       <c r="C715" t="s">
         <v>876</v>
@@ -31301,10 +31304,10 @@
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B716">
-        <v>2035</v>
+        <v>764</v>
       </c>
       <c r="C716" t="s">
         <v>876</v>
@@ -31312,10 +31315,10 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B717">
-        <v>900</v>
+        <v>2035</v>
       </c>
       <c r="C717" t="s">
         <v>876</v>
@@ -31323,10 +31326,10 @@
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B718">
-        <v>1172</v>
+        <v>900</v>
       </c>
       <c r="C718" t="s">
         <v>876</v>
@@ -31334,10 +31337,10 @@
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B719">
-        <v>962</v>
+        <v>1172</v>
       </c>
       <c r="C719" t="s">
         <v>876</v>
@@ -31345,10 +31348,10 @@
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B720">
-        <v>2494</v>
+        <v>962</v>
       </c>
       <c r="C720" t="s">
         <v>876</v>
@@ -31356,10 +31359,10 @@
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B721">
-        <v>8025</v>
+        <v>2494</v>
       </c>
       <c r="C721" t="s">
         <v>876</v>
@@ -31367,10 +31370,10 @@
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B722">
-        <v>1015</v>
+        <v>8025</v>
       </c>
       <c r="C722" t="s">
         <v>876</v>
@@ -31378,21 +31381,21 @@
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>1268</v>
+        <v>879</v>
       </c>
       <c r="B723">
-        <v>310</v>
+        <v>1015</v>
       </c>
       <c r="C723" t="s">
-        <v>1274</v>
+        <v>876</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B724">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C724" t="s">
         <v>1274</v>
@@ -31400,10 +31403,10 @@
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B725">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C725" t="s">
         <v>1274</v>
@@ -31411,10 +31414,10 @@
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B726">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C726" t="s">
         <v>1274</v>
@@ -31422,10 +31425,10 @@
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B727">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C727" t="s">
         <v>1274</v>
@@ -31433,10 +31436,10 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B728">
-        <v>2798</v>
+        <v>311</v>
       </c>
       <c r="C728" t="s">
         <v>1274</v>
@@ -31444,10 +31447,10 @@
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B729">
-        <v>12</v>
+        <v>2798</v>
       </c>
       <c r="C729" t="s">
         <v>1274</v>
@@ -31455,10 +31458,10 @@
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B730">
-        <v>2797</v>
+        <v>12</v>
       </c>
       <c r="C730" t="s">
         <v>1274</v>
@@ -31466,21 +31469,21 @@
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>1620</v>
+        <v>1275</v>
       </c>
       <c r="B731">
-        <v>3977</v>
+        <v>2797</v>
       </c>
       <c r="C731" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>1276</v>
+        <v>1620</v>
       </c>
       <c r="B732">
-        <v>1998</v>
+        <v>3977</v>
       </c>
       <c r="C732" t="s">
         <v>1276</v>
@@ -31488,21 +31491,21 @@
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B733">
-        <v>5905</v>
+        <v>1998</v>
       </c>
       <c r="C733" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B734">
-        <v>973</v>
+        <v>5905</v>
       </c>
       <c r="C734" t="s">
         <v>1278</v>
@@ -31510,21 +31513,21 @@
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>880</v>
+        <v>1278</v>
       </c>
       <c r="B735">
-        <v>6570</v>
+        <v>973</v>
       </c>
       <c r="C735" t="s">
-        <v>881</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B736">
-        <v>3267</v>
+        <v>6570</v>
       </c>
       <c r="C736" t="s">
         <v>881</v>
@@ -31532,10 +31535,10 @@
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B737">
-        <v>986</v>
+        <v>3267</v>
       </c>
       <c r="C737" t="s">
         <v>881</v>
@@ -31543,21 +31546,21 @@
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>1279</v>
+        <v>882</v>
       </c>
       <c r="B738">
-        <v>31</v>
+        <v>986</v>
       </c>
       <c r="C738" t="s">
-        <v>1290</v>
+        <v>881</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B739">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C739" t="s">
         <v>1290</v>
@@ -31565,10 +31568,10 @@
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B740">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C740" t="s">
         <v>1290</v>
@@ -31576,10 +31579,10 @@
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B741">
-        <v>1157</v>
+        <v>51</v>
       </c>
       <c r="C741" t="s">
         <v>1290</v>
@@ -31587,10 +31590,10 @@
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B742">
-        <v>2187</v>
+        <v>1157</v>
       </c>
       <c r="C742" t="s">
         <v>1290</v>
@@ -31598,10 +31601,10 @@
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B743">
-        <v>50</v>
+        <v>2187</v>
       </c>
       <c r="C743" t="s">
         <v>1290</v>
@@ -31609,10 +31612,10 @@
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B744">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C744" t="s">
         <v>1290</v>
@@ -31620,10 +31623,10 @@
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B745">
-        <v>4225</v>
+        <v>33</v>
       </c>
       <c r="C745" t="s">
         <v>1290</v>
@@ -31631,10 +31634,10 @@
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B746">
-        <v>177</v>
+        <v>4225</v>
       </c>
       <c r="C746" t="s">
         <v>1290</v>
@@ -31642,10 +31645,10 @@
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B747">
-        <v>1156</v>
+        <v>177</v>
       </c>
       <c r="C747" t="s">
         <v>1290</v>
@@ -31653,10 +31656,10 @@
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>897</v>
+        <v>1288</v>
       </c>
       <c r="B748">
-        <v>45</v>
+        <v>1156</v>
       </c>
       <c r="C748" t="s">
         <v>1290</v>
@@ -31664,10 +31667,10 @@
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>1289</v>
+        <v>897</v>
       </c>
       <c r="B749">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C749" t="s">
         <v>1290</v>
@@ -31675,10 +31678,10 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B750">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C750" t="s">
         <v>1290</v>
@@ -31686,10 +31689,10 @@
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B751">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C751" t="s">
         <v>1290</v>
@@ -31697,10 +31700,10 @@
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B752">
-        <v>3578</v>
+        <v>46</v>
       </c>
       <c r="C752" t="s">
         <v>1290</v>
@@ -31708,21 +31711,21 @@
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B753">
-        <v>2598</v>
+        <v>3578</v>
       </c>
       <c r="C753" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B754">
-        <v>3792</v>
+        <v>2598</v>
       </c>
       <c r="C754" t="s">
         <v>1295</v>
@@ -31730,10 +31733,10 @@
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B755">
-        <v>1938</v>
+        <v>3792</v>
       </c>
       <c r="C755" t="s">
         <v>1295</v>
@@ -31741,21 +31744,21 @@
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>1621</v>
+        <v>1295</v>
       </c>
       <c r="B756">
-        <v>6584</v>
+        <v>1938</v>
       </c>
       <c r="C756" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>1296</v>
+        <v>1621</v>
       </c>
       <c r="B757">
-        <v>44</v>
+        <v>6584</v>
       </c>
       <c r="C757" t="s">
         <v>1300</v>
@@ -31763,10 +31766,10 @@
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B758">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C758" t="s">
         <v>1300</v>
@@ -31774,10 +31777,10 @@
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>1622</v>
+        <v>1297</v>
       </c>
       <c r="B759">
-        <v>6586</v>
+        <v>40</v>
       </c>
       <c r="C759" t="s">
         <v>1300</v>
@@ -31785,10 +31788,10 @@
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>1298</v>
+        <v>1622</v>
       </c>
       <c r="B760">
-        <v>3412</v>
+        <v>6586</v>
       </c>
       <c r="C760" t="s">
         <v>1300</v>
@@ -31796,10 +31799,10 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>1623</v>
+        <v>1298</v>
       </c>
       <c r="B761">
-        <v>6587</v>
+        <v>3412</v>
       </c>
       <c r="C761" t="s">
         <v>1300</v>
@@ -31807,10 +31810,10 @@
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B762">
-        <v>6585</v>
+        <v>6587</v>
       </c>
       <c r="C762" t="s">
         <v>1300</v>
@@ -31818,10 +31821,10 @@
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B763">
-        <v>39</v>
+        <v>6585</v>
       </c>
       <c r="C763" t="s">
         <v>1300</v>
@@ -31829,10 +31832,10 @@
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>1299</v>
+        <v>1625</v>
       </c>
       <c r="B764">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C764" t="s">
         <v>1300</v>
@@ -31840,10 +31843,10 @@
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>1626</v>
+        <v>1299</v>
       </c>
       <c r="B765">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C765" t="s">
         <v>1300</v>
@@ -31851,10 +31854,10 @@
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>1300</v>
+        <v>1626</v>
       </c>
       <c r="B766">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C766" t="s">
         <v>1300</v>
@@ -31862,10 +31865,10 @@
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>1627</v>
+        <v>1300</v>
       </c>
       <c r="B767">
-        <v>6583</v>
+        <v>37</v>
       </c>
       <c r="C767" t="s">
         <v>1300</v>
@@ -31873,21 +31876,21 @@
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>1301</v>
+        <v>1627</v>
       </c>
       <c r="B768">
-        <v>403</v>
+        <v>6583</v>
       </c>
       <c r="C768" t="s">
-        <v>1630</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B769">
-        <v>4720</v>
+        <v>403</v>
       </c>
       <c r="C769" t="s">
         <v>1630</v>
@@ -31895,10 +31898,10 @@
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>705</v>
+        <v>1302</v>
       </c>
       <c r="B770">
-        <v>16</v>
+        <v>4720</v>
       </c>
       <c r="C770" t="s">
         <v>1630</v>
@@ -31906,10 +31909,10 @@
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>1303</v>
+        <v>705</v>
       </c>
       <c r="B771">
-        <v>4721</v>
+        <v>16</v>
       </c>
       <c r="C771" t="s">
         <v>1630</v>
@@ -31917,10 +31920,10 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B772">
-        <v>462</v>
+        <v>4721</v>
       </c>
       <c r="C772" t="s">
         <v>1630</v>
@@ -31928,10 +31931,10 @@
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>1628</v>
+        <v>1304</v>
       </c>
       <c r="B773">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="C773" t="s">
         <v>1630</v>
@@ -31939,10 +31942,10 @@
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
-        <v>1305</v>
+        <v>1628</v>
       </c>
       <c r="B774">
-        <v>4726</v>
+        <v>399</v>
       </c>
       <c r="C774" t="s">
         <v>1630</v>
@@ -31950,10 +31953,10 @@
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B775">
-        <v>6049</v>
+        <v>4726</v>
       </c>
       <c r="C775" t="s">
         <v>1630</v>
@@ -31961,10 +31964,10 @@
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B776">
-        <v>4731</v>
+        <v>6049</v>
       </c>
       <c r="C776" t="s">
         <v>1630</v>
@@ -31972,10 +31975,10 @@
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B777">
-        <v>4744</v>
+        <v>4731</v>
       </c>
       <c r="C777" t="s">
         <v>1630</v>
@@ -31983,10 +31986,10 @@
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B778">
-        <v>4748</v>
+        <v>4744</v>
       </c>
       <c r="C778" t="s">
         <v>1630</v>
@@ -31994,10 +31997,10 @@
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B779">
-        <v>468</v>
+        <v>4748</v>
       </c>
       <c r="C779" t="s">
         <v>1630</v>
@@ -32005,10 +32008,10 @@
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B780">
-        <v>401</v>
+        <v>468</v>
       </c>
       <c r="C780" t="s">
         <v>1630</v>
@@ -32016,10 +32019,10 @@
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B781">
-        <v>15</v>
+        <v>401</v>
       </c>
       <c r="C781" t="s">
         <v>1630</v>
@@ -32027,18 +32030,29 @@
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B782">
-        <v>6050</v>
+        <v>15</v>
       </c>
       <c r="C782" t="s">
         <v>1630</v>
       </c>
     </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B783">
+        <v>6050</v>
+      </c>
+      <c r="C783" t="s">
+        <v>1630</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C782">
-    <sortCondition ref="C2:C782"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C783">
+    <sortCondition ref="C2:C783"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
